--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -1694,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2126"/>
+  <dimension ref="A1:P2220"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.83203125" customWidth="1"/>
@@ -24522,8 +24522,17 @@
       <c r="A953" t="s">
         <v>5</v>
       </c>
-      <c r="B953" t="s">
-        <v>433</v>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="954" spans="1:16" x14ac:dyDescent="0.2">
@@ -24649,8 +24658,15 @@
       <c r="J961">
         <v>0.54930614433405478</v>
       </c>
-      <c r="L961" t="s">
-        <v>196</v>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
       <c r="M961">
         <v>0</v>
@@ -25658,20 +25674,26 @@
       </c>
     </row>
     <row r="990" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A990" t="s">
-        <v>225</v>
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="B990">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C990" t="s">
         <v>54</v>
       </c>
-      <c r="D990" t="s">
-        <v>70</v>
-      </c>
-      <c r="E990" t="s">
-        <v>51</v>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F990" t="s">
         <v>47</v>
@@ -25683,22 +25705,33 @@
         <v>2</v>
       </c>
       <c r="I990">
-        <v>-0.51082562376599072</v>
+        <v>0.0</v>
       </c>
       <c r="J990">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L990" t="s">
-        <v>226</v>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
       <c r="M990">
         <v>0</v>
       </c>
-      <c r="N990" t="s">
-        <v>227</v>
-      </c>
-      <c r="O990" t="s">
-        <v>227</v>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+      <c r="O990" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="P990" t="s">
         <v>403</v>
@@ -26092,8 +26125,17 @@
       <c r="A1001" t="s">
         <v>5</v>
       </c>
-      <c r="B1001" t="s">
-        <v>433</v>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1002" spans="1:16" x14ac:dyDescent="0.2">
@@ -26219,8 +26261,15 @@
       <c r="J1009">
         <v>0.54930614433405478</v>
       </c>
-      <c r="L1009" t="s">
-        <v>196</v>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
       <c r="M1009">
         <v>0</v>
@@ -27228,20 +27277,26 @@
       </c>
     </row>
     <row r="1038" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1038" t="s">
-        <v>225</v>
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="B1038">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C1038" t="s">
         <v>54</v>
       </c>
-      <c r="D1038" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1038" t="s">
-        <v>51</v>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F1038" t="s">
         <v>47</v>
@@ -27253,22 +27308,33 @@
         <v>2</v>
       </c>
       <c r="I1038">
-        <v>-0.51082562376599072</v>
+        <v>0.0</v>
       </c>
       <c r="J1038">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1038" t="s">
-        <v>226</v>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
       <c r="M1038">
         <v>0</v>
       </c>
-      <c r="N1038" t="s">
-        <v>227</v>
-      </c>
-      <c r="O1038" t="s">
-        <v>227</v>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+      <c r="O1038" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="P1038" t="s">
         <v>403</v>
@@ -46281,8 +46347,17 @@
       <c r="A1856" t="s">
         <v>5</v>
       </c>
-      <c r="B1856" t="s">
-        <v>433</v>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1857" spans="1:14" x14ac:dyDescent="0.2">
@@ -46402,8 +46477,15 @@
       <c r="J1864">
         <v>0.3465735902799727</v>
       </c>
-      <c r="L1864" t="s">
-        <v>198</v>
+      <c r="L1864" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
     </row>
     <row r="1865" spans="1:14" x14ac:dyDescent="0.2">
@@ -47353,20 +47435,26 @@
       </c>
     </row>
     <row r="1894" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1894" t="s">
-        <v>225</v>
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="B1894">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C1894" t="s">
         <v>54</v>
       </c>
-      <c r="D1894" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1894" t="s">
-        <v>51</v>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F1894" t="s">
         <v>47</v>
@@ -47378,16 +47466,25 @@
         <v>2</v>
       </c>
       <c r="I1894">
-        <v>-0.51082562376599072</v>
+        <v>0.0</v>
       </c>
       <c r="J1894">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1894" t="s">
-        <v>226</v>
-      </c>
-      <c r="N1894" t="s">
-        <v>227</v>
+      <c r="L1894" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+      <c r="N1894" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
     </row>
     <row r="1895" spans="1:14" x14ac:dyDescent="0.2">
@@ -47715,8 +47812,17 @@
       <c r="A1905" t="s">
         <v>5</v>
       </c>
-      <c r="B1905" t="s">
-        <v>433</v>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1906" spans="1:14" x14ac:dyDescent="0.2">
@@ -47836,8 +47942,15 @@
       <c r="J1913">
         <v>0.3465735902799727</v>
       </c>
-      <c r="L1913" t="s">
-        <v>198</v>
+      <c r="L1913" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
       </c>
     </row>
     <row r="1914" spans="1:14" x14ac:dyDescent="0.2">
@@ -48787,20 +48900,26 @@
       </c>
     </row>
     <row r="1943" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1943" t="s">
-        <v>225</v>
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
       <c r="B1943">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="C1943" t="s">
         <v>54</v>
       </c>
-      <c r="D1943" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1943" t="s">
-        <v>51</v>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
       </c>
       <c r="F1943" t="s">
         <v>47</v>
@@ -48812,16 +48931,25 @@
         <v>2</v>
       </c>
       <c r="I1943">
-        <v>-0.51082562376599072</v>
+        <v>0.0</v>
       </c>
       <c r="J1943">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1943" t="s">
-        <v>226</v>
-      </c>
-      <c r="N1943" t="s">
-        <v>227</v>
+      <c r="L1943" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+      <c r="N1943" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
       </c>
     </row>
     <row r="1944" spans="1:14" x14ac:dyDescent="0.2">
@@ -54188,6 +54316,2076 @@
       </c>
       <c r="N2126" t="s">
         <v>319</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B2129" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B2130" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B2131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B2132" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B2133" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2134" t="inlineStr">
+        <is>
+          <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B2135" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2137" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C2137" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D2137" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E2137" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F2137" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G2137" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H2137" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I2137" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+      <c r="B2138">
+        <v>1</v>
+      </c>
+      <c r="C2138" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2138" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2138" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G2138" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+      <c r="I2138" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" t="inlineStr">
+        <is>
+          <t>market for zirconium oxide</t>
+        </is>
+      </c>
+      <c r="B2139">
+        <v>1.4218557443332087</v>
+      </c>
+      <c r="C2139" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2139" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2139" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2139" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+      <c r="I2139" t="inlineStr">
+        <is>
+          <t>zirconium oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B2140">
+        <v>0.27718928998370695</v>
+      </c>
+      <c r="C2140" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2140" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2140" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2140" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I2140" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B2141">
+        <v>1.6362268470439452</v>
+      </c>
+      <c r="C2141" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2141" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2141" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2141" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I2141" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" t="inlineStr">
+        <is>
+          <t>market for magnesium</t>
+        </is>
+      </c>
+      <c r="B2142">
+        <v>0.5609096405839644</v>
+      </c>
+      <c r="C2142" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2142" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2142" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2142" t="inlineStr">
+        <is>
+          <t>magnesium</t>
+        </is>
+      </c>
+      <c r="I2142" t="inlineStr">
+        <is>
+          <t>magnesium</t>
+        </is>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B2143">
+        <v>0.3692241653858403</v>
+      </c>
+      <c r="C2143" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2143" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2143" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2143" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I2143" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2144">
+        <v>10</v>
+      </c>
+      <c r="C2144" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2144" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2144" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2144" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2144" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2145">
+      <c r="A2145" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B2145">
+        <v>30</v>
+      </c>
+      <c r="C2145" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2145" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F2145" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2145" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I2145" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2146">
+      <c r="A2146" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B2146">
+        <v>-2.249768066575278</v>
+      </c>
+      <c r="C2146" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2146" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2146" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2146" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I2146" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2147">
+      <c r="A2147" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B2147">
+        <v>1.0156376207553877</v>
+      </c>
+      <c r="D2147" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E2147" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F2147" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H2147" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2150">
+      <c r="A2150" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B2150" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B2151" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B2152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B2153" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B2154" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2155" t="inlineStr">
+        <is>
+          <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B2156" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C2158" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D2158" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E2158" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F2158" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G2158" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H2158" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I2158" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+      <c r="B2159">
+        <v>1</v>
+      </c>
+      <c r="C2159" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2159" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2159" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G2159" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+      <c r="I2159" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
+        <is>
+          <t>market for ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+      <c r="B2160">
+        <v>1.5151515151515151</v>
+      </c>
+      <c r="C2160" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2160" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2160" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2160" t="inlineStr">
+        <is>
+          <t>ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+      <c r="I2160" t="inlineStr">
+        <is>
+          <t>ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B2161">
+        <v>-0.5151515151515151</v>
+      </c>
+      <c r="C2161" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2161" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2161" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2161" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I2161" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2162">
+      <c r="A2162" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2162">
+        <v>5</v>
+      </c>
+      <c r="C2162" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2162" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2162" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2162" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2162" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B2165" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B2166" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B2167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B2168" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B2169" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2170" t="inlineStr">
+        <is>
+          <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B2171" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2173" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C2173" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D2173" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E2173" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F2173" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G2173" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H2173" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I2173" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+      <c r="B2174">
+        <v>1</v>
+      </c>
+      <c r="C2174" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2174" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2174" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G2174" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+      <c r="I2174" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+      <c r="B2175">
+        <v>0.9884</v>
+      </c>
+      <c r="C2175" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2175" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2175" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2175" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+      <c r="I2175" t="inlineStr">
+        <is>
+          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+      <c r="B2176">
+        <v>0.01</v>
+      </c>
+      <c r="C2176" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2176" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2176" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2176" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+      <c r="I2176" t="inlineStr">
+        <is>
+          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" t="inlineStr">
+        <is>
+          <t>market for steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="B2177">
+        <v>0.00035</v>
+      </c>
+      <c r="C2177" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2177" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2177" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2177" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="I2177" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" t="inlineStr">
+        <is>
+          <t>market for oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="B2178">
+        <v>0.00125</v>
+      </c>
+      <c r="C2178" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2178" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2178" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2178" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+      <c r="I2178" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2179">
+        <v>1</v>
+      </c>
+      <c r="C2179" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2179" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2179" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2179" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2179" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B2180">
+        <v>3</v>
+      </c>
+      <c r="C2180" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2180" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F2180" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2180" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I2180" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="B2181">
+        <v>1</v>
+      </c>
+      <c r="C2181" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2181" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2181" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2181" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="I2181" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B2184" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B2185" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B2186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B2187" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B2188" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2189" t="inlineStr">
+        <is>
+          <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B2190" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2192" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C2192" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D2192" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E2192" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F2192" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G2192" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H2192" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I2192" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+      <c r="B2193">
+        <v>1</v>
+      </c>
+      <c r="C2193" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2193" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2193" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G2193" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+      <c r="I2193" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B2194">
+        <v>0.525</v>
+      </c>
+      <c r="C2194" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2194" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2194" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2194" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I2194" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
+        <is>
+          <t>market for chromium</t>
+        </is>
+      </c>
+      <c r="B2195">
+        <v>0.19</v>
+      </c>
+      <c r="C2195" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2195" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2195" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2195" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+      <c r="I2195" t="inlineStr">
+        <is>
+          <t>chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
+        <is>
+          <t>market for ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+      <c r="B2196">
+        <v>0.07765151515151514</v>
+      </c>
+      <c r="C2196" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2196" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2196" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2196" t="inlineStr">
+        <is>
+          <t>ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+      <c r="I2196" t="inlineStr">
+        <is>
+          <t>ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" t="inlineStr">
+        <is>
+          <t>market for molybdenum</t>
+        </is>
+      </c>
+      <c r="B2197">
+        <v>0.0305</v>
+      </c>
+      <c r="C2197" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2197" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2197" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2197" t="inlineStr">
+        <is>
+          <t>molybdenum</t>
+        </is>
+      </c>
+      <c r="I2197" t="inlineStr">
+        <is>
+          <t>molybdenum</t>
+        </is>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" t="inlineStr">
+        <is>
+          <t>market for titanium</t>
+        </is>
+      </c>
+      <c r="B2198">
+        <v>0.009</v>
+      </c>
+      <c r="C2198" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2198" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2198" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2198" t="inlineStr">
+        <is>
+          <t>titanium</t>
+        </is>
+      </c>
+      <c r="I2198" t="inlineStr">
+        <is>
+          <t>titanium</t>
+        </is>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" t="inlineStr">
+        <is>
+          <t>market for aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="B2199">
+        <v>0.005</v>
+      </c>
+      <c r="C2199" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2199" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2199" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2199" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+      <c r="I2199" t="inlineStr">
+        <is>
+          <t>aluminium, primary, ingot</t>
+        </is>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B2200">
+        <v>0.0004</v>
+      </c>
+      <c r="C2200" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2200" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2200" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2200" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I2200" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" t="inlineStr">
+        <is>
+          <t>market for steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="B2201">
+        <v>0.16244848484848481</v>
+      </c>
+      <c r="C2201" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2201" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2201" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2201" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="I2201" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2202">
+        <v>1</v>
+      </c>
+      <c r="C2202" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2202" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2202" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2202" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2202" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B2203">
+        <v>3</v>
+      </c>
+      <c r="C2203" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2203" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F2203" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2203" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I2203" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="B2204">
+        <v>1</v>
+      </c>
+      <c r="C2204" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2204" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2204" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2204" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="I2204" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B2207" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B2208" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B2209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B2210" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B2211" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B2212" t="inlineStr">
+        <is>
+          <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
+        </is>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B2213" t="inlineStr">
+        <is>
+          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
+The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
+M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
+Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
+SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B2215" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C2215" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D2215" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E2215" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F2215" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G2215" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H2215" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I2215" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+      <c r="B2216">
+        <v>1</v>
+      </c>
+      <c r="C2216" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2216" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F2216" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G2216" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+      <c r="I2216" t="inlineStr">
+        <is>
+          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+      <c r="B2217">
+        <v>0.30714691943127964</v>
+      </c>
+      <c r="C2217" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2217" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2217" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2217" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+      <c r="I2217" t="inlineStr">
+        <is>
+          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+      <c r="B2218">
+        <v>0.008265402843601895</v>
+      </c>
+      <c r="C2218" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2218" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2218" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2218" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+      <c r="I2218" t="inlineStr">
+        <is>
+          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
+        <is>
+          <t>market for steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="B2219">
+        <v>0.02767772511848341</v>
+      </c>
+      <c r="C2219" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2219" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2219" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2219" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+      <c r="I2219" t="inlineStr">
+        <is>
+          <t>steel, chromium steel 18/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
+        <is>
+          <t>market for aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="B2220">
+        <v>0.0011279620853080568</v>
+      </c>
+      <c r="C2220" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2220" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2220" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2220" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
+      </c>
+      <c r="I2220" t="inlineStr">
+        <is>
+          <t>aluminium oxide, non-metallurgical</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -46349,7 +46349,12 @@
       </c>
       <c r="B1856" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -46479,12 +46484,10 @@
       </c>
       <c r="L1864" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
-Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
-The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
-M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
-Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
-SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
         </is>
       </c>
     </row>
@@ -47325,7 +47328,7 @@
         <v>430</v>
       </c>
       <c r="B1891">
-        <v>7.15</v>
+        <v>1</v>
       </c>
       <c r="C1891" t="s">
         <v>46</v>
@@ -47346,13 +47349,18 @@
         <v>2</v>
       </c>
       <c r="I1891">
-        <v>1.9671123567059161</v>
+        <v>0.0</v>
       </c>
       <c r="J1891">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1891" t="s">
-        <v>259</v>
+      <c r="L1891" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
+        </is>
       </c>
       <c r="N1891" t="s">
         <v>430</v>
@@ -47814,7 +47822,12 @@
       </c>
       <c r="B1905" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -47944,12 +47957,10 @@
       </c>
       <c r="L1913" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
-Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
-The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
-M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
-Inconel718 nominal fractions {'Ni': 0.525, 'Cr': 0.19, 'Nb': 0.05125, 'Mo': 0.0305, 'Ti': 0.009, 'Al': 0.005, 'C': 0.0004, 'Fe': 0.18884999999999996} select values within published main-element ranges with Fe balance; unquantified minor impurities are not certified zero. FerroNb supplies Nb plus its associated Fe in this Fe-bearing alloy, with only remaining Fe supplied separately. 304L uses existing18/8 material proxy; exact low-carbon grade remains unresolved. Reference alloy melting/tube/spring forming uses1kWh+3MJ/kgfinished alloy and generic metal-working service, at100% alloy retention; these are engineering allowances, not manufacturer measured processes. Quantified gross losses need a separate source. No new end-of-life route is added to fuel manufacture: existing spent-fuel chain retains the irradiated assembly; its mass-reference conventions remain a separate boundary limitation. Existing workbook only; no native/runtime or primary/secondary-share changes.
-SUPPORTED-VERSION ZIRCONIUM SUPPLY: nuclear-grade sponge markets do not exist in ecoinvent3.8, so do not insert a broken supplier or replace Zr by Cr. Use one explicit common oxide-to-metal reference, based on documented Kroll chemistry: EP2766502A1 https://patents.google.com/patent/EP2766502A1/en and US5098471A https://patents.google.com/patent/US5098471A/en . Net ZrO2+2C+2Cl2+2Mg -&gt; Zr+2CO+2MgCl2, followed by CO oxidation with O2 to2CO2. At95% finished-metal retention feedkg={'ZrO2': 1.4218557443332087, 'C': 0.27718928998370695, 'Cl2': 1.6362268470439452, 'Mg': 0.5609096405839644, 'O2': 0.3692241653858403}; CO2=1.0156376207553877kg, MgCl2=2.19713648762791kg, Zr reject=0.05263157894736836kg. Generic hazardous solid/salt collection is an unvalidated fate proxy; no salt or Mg recovery credit. Use10kWh+30MJ/kgmetal as explicit combined chlorination/reduction/distillation utility allowance, not measured vendor data; sensitivity5-50kWh,10-100MJ and90-100%yield. Hafnium separation, semiconductor/nuclear purity, solvent chemistry, Mg/Cl recycling and actual emission control remain material coverage gaps, NOT certified zero burdens. Bulk oxide is a feed-grade proxy; this helper represents the element and net manufacturing chemistry without claiming to produce certified nuclear-grade material. The earlier nuclear-grade sponge wording specifies the required application, not certification of this engineering provider.</t>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
         </is>
       </c>
     </row>
@@ -48790,7 +48801,7 @@
         <v>431</v>
       </c>
       <c r="B1940">
-        <v>7.15</v>
+        <v>1</v>
       </c>
       <c r="C1940" t="s">
         <v>46</v>
@@ -48811,13 +48822,18 @@
         <v>2</v>
       </c>
       <c r="I1940">
-        <v>1.9671123567059161</v>
+        <v>0.0</v>
       </c>
       <c r="J1940">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1940" t="s">
-        <v>259</v>
+      <c r="L1940" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
+        </is>
       </c>
       <c r="N1940" t="s">
         <v>431</v>
@@ -49277,8 +49293,15 @@
       <c r="A1954" t="s">
         <v>5</v>
       </c>
-      <c r="B1954" t="s">
-        <v>433</v>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1955" spans="1:14" x14ac:dyDescent="0.2">
@@ -49375,7 +49398,7 @@
         <v>260</v>
       </c>
       <c r="B1962">
-        <v>1.1000000000000001E-3</v>
+        <v>0.007865</v>
       </c>
       <c r="C1962" t="s">
         <v>27</v>
@@ -49393,13 +49416,18 @@
         <v>2</v>
       </c>
       <c r="I1962">
-        <v>-6.812445099177812</v>
+        <v>-4.8453327424718955</v>
       </c>
       <c r="J1962">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L1962" t="s">
-        <v>261</v>
+      <c r="L1962" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
+        </is>
       </c>
     </row>
     <row r="1963" spans="1:14" x14ac:dyDescent="0.2">
@@ -49407,7 +49435,7 @@
         <v>262</v>
       </c>
       <c r="B1963">
-        <v>3.8E-6</v>
+        <v>2.7170000000000002e-05</v>
       </c>
       <c r="C1963" t="s">
         <v>27</v>
@@ -49425,7 +49453,7 @@
         <v>2</v>
       </c>
       <c r="I1963">
-        <v>-12.480509491231929</v>
+        <v>-10.513397134526018</v>
       </c>
       <c r="J1963">
         <v>4.7655089902162509E-2</v>
@@ -49439,7 +49467,7 @@
         <v>263</v>
       </c>
       <c r="B1964">
-        <v>1.3E-6</v>
+        <v>9.295000000000002e-06</v>
       </c>
       <c r="C1964" t="s">
         <v>27</v>
@@ -49457,7 +49485,7 @@
         <v>2</v>
       </c>
       <c r="I1964">
-        <v>-13.553146293496781</v>
+        <v>-11.586033936790866</v>
       </c>
       <c r="J1964">
         <v>4.7655089902162509E-2</v>
@@ -49471,7 +49499,7 @@
         <v>264</v>
       </c>
       <c r="B1965">
-        <v>1.2999999999999999E-5</v>
+        <v>9.295e-05</v>
       </c>
       <c r="C1965" t="s">
         <v>27</v>
@@ -49489,7 +49517,7 @@
         <v>2</v>
       </c>
       <c r="I1965">
-        <v>-11.250561200502739</v>
+        <v>-9.28344884379682</v>
       </c>
       <c r="J1965">
         <v>0.13118213223374561</v>
@@ -49503,7 +49531,7 @@
         <v>266</v>
       </c>
       <c r="B1966">
-        <v>1.2999999999999999E-3</v>
+        <v>0.009295</v>
       </c>
       <c r="C1966" t="s">
         <v>27</v>
@@ -49521,7 +49549,7 @@
         <v>2</v>
       </c>
       <c r="I1966">
-        <v>-6.6453910145146464</v>
+        <v>-4.67827865780873</v>
       </c>
       <c r="J1966">
         <v>4.7655089902162509E-2</v>
@@ -49535,7 +49563,7 @@
         <v>204</v>
       </c>
       <c r="B1967">
-        <v>1.1E-4</v>
+        <v>0.0007865000000000001</v>
       </c>
       <c r="C1967" t="s">
         <v>27</v>
@@ -49553,7 +49581,7 @@
         <v>2</v>
       </c>
       <c r="I1967">
-        <v>-9.1150301921718579</v>
+        <v>-7.147917835465941</v>
       </c>
       <c r="J1967">
         <v>4.7655089902162509E-2</v>
@@ -49567,7 +49595,7 @@
         <v>32</v>
       </c>
       <c r="B1968">
-        <v>126</v>
+        <v>900.9000000000001</v>
       </c>
       <c r="C1968" t="s">
         <v>27</v>
@@ -49585,7 +49613,7 @@
         <v>2</v>
       </c>
       <c r="I1968">
-        <v>4.836281906951478</v>
+        <v>6.8033942636573945</v>
       </c>
       <c r="J1968">
         <v>4.7655089902162509E-2</v>
@@ -49599,7 +49627,7 @@
         <v>268</v>
       </c>
       <c r="B1969">
-        <v>6.0999999999999999E-5</v>
+        <v>0.00043615</v>
       </c>
       <c r="C1969" t="s">
         <v>27</v>
@@ -49617,7 +49645,7 @@
         <v>2</v>
       </c>
       <c r="I1969">
-        <v>-9.7046366937909632</v>
+        <v>-7.737524337085047</v>
       </c>
       <c r="J1969">
         <v>4.7655089902162509E-2</v>
@@ -49631,7 +49659,7 @@
         <v>269</v>
       </c>
       <c r="B1970">
-        <v>3.7E-8</v>
+        <v>2.6455e-07</v>
       </c>
       <c r="C1970" t="s">
         <v>27</v>
@@ -49649,7 +49677,7 @@
         <v>2</v>
       </c>
       <c r="I1970">
-        <v>-17.112347924302188</v>
+        <v>-15.14523556759627</v>
       </c>
       <c r="J1970">
         <v>4.7655089902162509E-2</v>
@@ -49663,7 +49691,7 @@
         <v>270</v>
       </c>
       <c r="B1971">
-        <v>2.5000000000000001E-3</v>
+        <v>0.017875000000000002</v>
       </c>
       <c r="C1971" t="s">
         <v>27</v>
@@ -49681,7 +49709,7 @@
         <v>2</v>
       </c>
       <c r="I1971">
-        <v>-5.9914645471079817</v>
+        <v>-4.024352190402065</v>
       </c>
       <c r="J1971">
         <v>4.7655089902162509E-2</v>
@@ -49695,7 +49723,7 @@
         <v>271</v>
       </c>
       <c r="B1972">
-        <v>3.4000000000000002E-4</v>
+        <v>0.0024310000000000004</v>
       </c>
       <c r="C1972" t="s">
         <v>27</v>
@@ -49713,7 +49741,7 @@
         <v>2</v>
       </c>
       <c r="I1972">
-        <v>-7.9865649403540671</v>
+        <v>-6.0194525836481505</v>
       </c>
       <c r="J1972">
         <v>4.7655089902162509E-2</v>
@@ -49727,7 +49755,7 @@
         <v>272</v>
       </c>
       <c r="B1973">
-        <v>2.2000000000000001E-6</v>
+        <v>1.573e-05</v>
       </c>
       <c r="C1973" t="s">
         <v>27</v>
@@ -49745,7 +49773,7 @@
         <v>2</v>
       </c>
       <c r="I1973">
-        <v>-13.027053197600001</v>
+        <v>-11.059940840894088</v>
       </c>
       <c r="J1973">
         <v>0.20273255405408211</v>
@@ -49759,7 +49787,7 @@
         <v>272</v>
       </c>
       <c r="B1974">
-        <v>3.0999999999999999E-3</v>
+        <v>0.022165</v>
       </c>
       <c r="C1974" t="s">
         <v>27</v>
@@ -49777,7 +49805,7 @@
         <v>2</v>
       </c>
       <c r="I1974">
-        <v>-5.7763531674910356</v>
+        <v>-3.8092408107851203</v>
       </c>
       <c r="J1974">
         <v>4.7655089902162509E-2</v>
@@ -49791,7 +49819,7 @@
         <v>257</v>
       </c>
       <c r="B1975">
-        <v>3.1000000000000001E-5</v>
+        <v>0.00022165000000000002</v>
       </c>
       <c r="C1975" t="s">
         <v>27</v>
@@ -49809,7 +49837,7 @@
         <v>2</v>
       </c>
       <c r="I1975">
-        <v>-10.38152335347913</v>
+        <v>-8.414410996773212</v>
       </c>
       <c r="J1975">
         <v>4.7655089902162509E-2</v>
@@ -49823,7 +49851,7 @@
         <v>257</v>
       </c>
       <c r="B1976">
-        <v>8.1999999999999994E-6</v>
+        <v>5.863e-05</v>
       </c>
       <c r="C1976" t="s">
         <v>27</v>
@@ -49841,7 +49869,7 @@
         <v>2</v>
       </c>
       <c r="I1976">
-        <v>-11.71137640369407</v>
+        <v>-9.74426404698815</v>
       </c>
       <c r="J1976">
         <v>4.7655089902162509E-2</v>
@@ -49855,7 +49883,7 @@
         <v>274</v>
       </c>
       <c r="B1977">
-        <v>3.8000000000000002E-5</v>
+        <v>0.00027170000000000004</v>
       </c>
       <c r="C1977" t="s">
         <v>27</v>
@@ -49873,7 +49901,7 @@
         <v>2</v>
       </c>
       <c r="I1977">
-        <v>-10.17792439823789</v>
+        <v>-8.210812041531971</v>
       </c>
       <c r="J1977">
         <v>4.7655089902162509E-2</v>
@@ -49919,7 +49947,7 @@
         <v>57</v>
       </c>
       <c r="B1979">
-        <v>2.5000000000000001E-5</v>
+        <v>0.00017875</v>
       </c>
       <c r="C1979" t="s">
         <v>54</v>
@@ -49940,7 +49968,7 @@
         <v>2</v>
       </c>
       <c r="I1979">
-        <v>-10.596634733096071</v>
+        <v>-8.629522376390158</v>
       </c>
       <c r="J1979">
         <v>4.7655089902162509E-2</v>
@@ -49957,7 +49985,7 @@
         <v>134</v>
       </c>
       <c r="B1980">
-        <v>0.05</v>
+        <v>0.35750000000000004</v>
       </c>
       <c r="C1980" t="s">
         <v>54</v>
@@ -49978,7 +50006,7 @@
         <v>2</v>
       </c>
       <c r="I1980">
-        <v>-2.9957322735539909</v>
+        <v>-1.0286199168480745</v>
       </c>
       <c r="J1980">
         <v>0.3465735902799727</v>
@@ -49995,7 +50023,7 @@
         <v>61</v>
       </c>
       <c r="B1981">
-        <v>1.8E-3</v>
+        <v>0.01287</v>
       </c>
       <c r="C1981" t="s">
         <v>54</v>
@@ -50016,7 +50044,7 @@
         <v>2</v>
       </c>
       <c r="I1981">
-        <v>-6.3199686140800182</v>
+        <v>-4.352856257374102</v>
       </c>
       <c r="J1981">
         <v>4.7655089902162509E-2</v>
@@ -50033,7 +50061,7 @@
         <v>64</v>
       </c>
       <c r="B1982">
-        <v>2.3999999999999998E-3</v>
+        <v>0.017159999999999998</v>
       </c>
       <c r="C1982" t="s">
         <v>54</v>
@@ -50054,7 +50082,7 @@
         <v>2</v>
       </c>
       <c r="I1982">
-        <v>-6.0322865416282374</v>
+        <v>-4.065174184922321</v>
       </c>
       <c r="J1982">
         <v>4.7655089902162509E-2</v>
@@ -50071,7 +50099,7 @@
         <v>276</v>
       </c>
       <c r="B1983">
-        <v>1.8E-3</v>
+        <v>0.01287</v>
       </c>
       <c r="C1983" t="s">
         <v>54</v>
@@ -50092,7 +50120,7 @@
         <v>2</v>
       </c>
       <c r="I1983">
-        <v>-6.3199686140800182</v>
+        <v>-4.352856257374102</v>
       </c>
       <c r="J1983">
         <v>0.3465735902799727</v>
@@ -50109,7 +50137,7 @@
         <v>76</v>
       </c>
       <c r="B1984">
-        <v>3.1099999999999999E-2</v>
+        <v>0.222365</v>
       </c>
       <c r="C1984" t="s">
         <v>54</v>
@@ -50130,7 +50158,7 @@
         <v>2</v>
       </c>
       <c r="I1984">
-        <v>-3.4705474597969488</v>
+        <v>-1.5034351030910322</v>
       </c>
       <c r="J1984">
         <v>4.7655089902162509E-2</v>
@@ -50147,7 +50175,7 @@
         <v>80</v>
       </c>
       <c r="B1985">
-        <v>8.1999999999999998E-4</v>
+        <v>0.005863</v>
       </c>
       <c r="C1985" t="s">
         <v>54</v>
@@ -50168,7 +50196,7 @@
         <v>2</v>
       </c>
       <c r="I1985">
-        <v>-7.1062062177059753</v>
+        <v>-5.139093861000059</v>
       </c>
       <c r="J1985">
         <v>4.7655089902162509E-2</v>
@@ -50185,7 +50213,7 @@
         <v>83</v>
       </c>
       <c r="B1986">
-        <v>2.9E-4</v>
+        <v>0.0020735000000000003</v>
       </c>
       <c r="C1986" t="s">
         <v>54</v>
@@ -50206,7 +50234,7 @@
         <v>2</v>
       </c>
       <c r="I1986">
-        <v>-8.145629634983754</v>
+        <v>-6.178517278277838</v>
       </c>
       <c r="J1986">
         <v>0.3465735902799727</v>
@@ -50223,7 +50251,7 @@
         <v>85</v>
       </c>
       <c r="B1987">
-        <v>0.6</v>
+        <v>4.29</v>
       </c>
       <c r="C1987" t="s">
         <v>54</v>
@@ -50244,7 +50272,7 @@
         <v>2</v>
       </c>
       <c r="I1987">
-        <v>-0.51082562376599072</v>
+        <v>1.4562867329399256</v>
       </c>
       <c r="J1987">
         <v>4.7655089902162509E-2</v>
@@ -50261,7 +50289,7 @@
         <v>278</v>
       </c>
       <c r="B1988">
-        <v>2.0000000000000001E-4</v>
+        <v>0.00143</v>
       </c>
       <c r="C1988" t="s">
         <v>54</v>
@@ -50282,7 +50310,7 @@
         <v>2</v>
       </c>
       <c r="I1988">
-        <v>-8.5171931914162382</v>
+        <v>-6.550080834710321</v>
       </c>
       <c r="J1988">
         <v>4.7655089902162509E-2</v>
@@ -50299,7 +50327,7 @@
         <v>280</v>
       </c>
       <c r="B1989">
-        <v>6.8000000000000005E-4</v>
+        <v>0.004862000000000001</v>
       </c>
       <c r="C1989" t="s">
         <v>54</v>
@@ -50320,7 +50348,7 @@
         <v>2</v>
       </c>
       <c r="I1989">
-        <v>-7.2934177597941217</v>
+        <v>-5.326305403088205</v>
       </c>
       <c r="J1989">
         <v>4.7655089902162509E-2</v>
@@ -50337,7 +50365,7 @@
         <v>90</v>
       </c>
       <c r="B1990">
-        <v>1.1E-5</v>
+        <v>7.865e-05</v>
       </c>
       <c r="C1990" t="s">
         <v>54</v>
@@ -50358,7 +50386,7 @@
         <v>2</v>
       </c>
       <c r="I1990">
-        <v>-11.417615285165899</v>
+        <v>-9.450502928459986</v>
       </c>
       <c r="J1990">
         <v>4.7655089902162509E-2</v>
@@ -50375,7 +50403,7 @@
         <v>228</v>
       </c>
       <c r="B1991">
-        <v>-3.0000000000000001E-6</v>
+        <v>-2.1450000000000003e-05</v>
       </c>
       <c r="C1991" t="s">
         <v>54</v>
@@ -50396,7 +50424,7 @@
         <v>2</v>
       </c>
       <c r="I1991">
-        <v>-12.716898269296159</v>
+        <v>-10.749785912590248</v>
       </c>
       <c r="J1991">
         <v>4.7655089902162509E-2</v>
@@ -50416,7 +50444,7 @@
         <v>92</v>
       </c>
       <c r="B1992">
-        <v>9.1999999999999998E-3</v>
+        <v>0.06578</v>
       </c>
       <c r="C1992" t="s">
         <v>54</v>
@@ -50437,7 +50465,7 @@
         <v>2</v>
       </c>
       <c r="I1992">
-        <v>-4.6885517949271422</v>
+        <v>-2.721439438221226</v>
       </c>
       <c r="J1992">
         <v>4.7655089902162509E-2</v>
@@ -50454,7 +50482,7 @@
         <v>282</v>
       </c>
       <c r="B1993">
-        <v>3.2000000000000003E-4</v>
+        <v>0.002288</v>
       </c>
       <c r="C1993" t="s">
         <v>54</v>
@@ -50475,7 +50503,7 @@
         <v>2</v>
       </c>
       <c r="I1993">
-        <v>-8.0471895621705016</v>
+        <v>-6.080077205464586</v>
       </c>
       <c r="J1993">
         <v>4.7655089902162509E-2</v>
@@ -50492,7 +50520,7 @@
         <v>284</v>
       </c>
       <c r="B1994">
-        <v>-0.23499999999999999</v>
+        <v>-1.68025</v>
       </c>
       <c r="C1994" t="s">
         <v>54</v>
@@ -50513,7 +50541,7 @@
         <v>2</v>
       </c>
       <c r="I1994">
-        <v>-1.4481697648379781</v>
+        <v>0.5189425918679382</v>
       </c>
       <c r="J1994">
         <v>4.7655089902162509E-2</v>
@@ -50533,7 +50561,7 @@
         <v>286</v>
       </c>
       <c r="B1995">
-        <v>1.5E-3</v>
+        <v>0.010725</v>
       </c>
       <c r="C1995" t="s">
         <v>54</v>
@@ -50554,7 +50582,7 @@
         <v>2</v>
       </c>
       <c r="I1995">
-        <v>-6.5022901708739722</v>
+        <v>-4.5351778141680565</v>
       </c>
       <c r="J1995">
         <v>4.7655089902162509E-2</v>
@@ -50571,7 +50599,7 @@
         <v>96</v>
       </c>
       <c r="B1996">
-        <v>3.8999999999999999E-4</v>
+        <v>0.0027885</v>
       </c>
       <c r="C1996" t="s">
         <v>54</v>
@@ -50592,7 +50620,7 @@
         <v>2</v>
       </c>
       <c r="I1996">
-        <v>-7.8493638188405823</v>
+        <v>-5.882251462134666</v>
       </c>
       <c r="J1996">
         <v>4.7655089902162509E-2</v>
@@ -50609,7 +50637,7 @@
         <v>100</v>
       </c>
       <c r="B1997">
-        <v>3.6000000000000001E-5</v>
+        <v>0.0002574</v>
       </c>
       <c r="C1997" t="s">
         <v>54</v>
@@ -50630,7 +50658,7 @@
         <v>2</v>
       </c>
       <c r="I1997">
-        <v>-10.231991619508159</v>
+        <v>-8.264879262802248</v>
       </c>
       <c r="J1997">
         <v>4.7655089902162509E-2</v>
@@ -50647,7 +50675,7 @@
         <v>289</v>
       </c>
       <c r="B1998">
-        <v>1.2E-4</v>
+        <v>0.000858</v>
       </c>
       <c r="C1998" t="s">
         <v>54</v>
@@ -50668,7 +50696,7 @@
         <v>2</v>
       </c>
       <c r="I1998">
-        <v>-9.0280188151822287</v>
+        <v>-7.060906458476312</v>
       </c>
       <c r="J1998">
         <v>4.7655089902162509E-2</v>
@@ -50685,7 +50713,7 @@
         <v>148</v>
       </c>
       <c r="B1999">
-        <v>8.7000000000000001E-4</v>
+        <v>0.0062205</v>
       </c>
       <c r="C1999" t="s">
         <v>54</v>
@@ -50706,7 +50734,7 @@
         <v>2</v>
       </c>
       <c r="I1999">
-        <v>-7.0470173463156449</v>
+        <v>-5.079904989609728</v>
       </c>
       <c r="J1999">
         <v>4.7655089902162509E-2</v>
@@ -50723,7 +50751,7 @@
         <v>291</v>
       </c>
       <c r="B2000">
-        <v>8.8000000000000003E-4</v>
+        <v>0.006292000000000001</v>
       </c>
       <c r="C2000" t="s">
         <v>54</v>
@@ -50744,7 +50772,7 @@
         <v>2</v>
       </c>
       <c r="I2000">
-        <v>-7.0355886504920218</v>
+        <v>-5.068476293786105</v>
       </c>
       <c r="J2000">
         <v>4.7655089902162509E-2</v>
@@ -50761,7 +50789,7 @@
         <v>293</v>
       </c>
       <c r="B2001">
-        <v>2.8E-3</v>
+        <v>0.02002</v>
       </c>
       <c r="C2001" t="s">
         <v>54</v>
@@ -50782,7 +50810,7 @@
         <v>2</v>
       </c>
       <c r="I2001">
-        <v>-5.8781358618009776</v>
+        <v>-3.9110235050950624</v>
       </c>
       <c r="J2001">
         <v>4.7655089902162509E-2</v>
@@ -50799,7 +50827,7 @@
         <v>295</v>
       </c>
       <c r="B2002">
-        <v>5.8000000000000003E-2</v>
+        <v>0.41470000000000007</v>
       </c>
       <c r="C2002" t="s">
         <v>54</v>
@@ -50820,7 +50848,7 @@
         <v>2</v>
       </c>
       <c r="I2002">
-        <v>-2.8473122684357182</v>
+        <v>-0.8801999117298013</v>
       </c>
       <c r="J2002">
         <v>4.7655089902162509E-2</v>
@@ -50837,7 +50865,7 @@
         <v>108</v>
       </c>
       <c r="B2003">
-        <v>0.15</v>
+        <v>1.0725</v>
       </c>
       <c r="C2003" t="s">
         <v>54</v>
@@ -50858,7 +50886,7 @@
         <v>2</v>
       </c>
       <c r="I2003">
-        <v>-1.8971199848858811</v>
+        <v>0.069992371820035</v>
       </c>
       <c r="J2003">
         <v>0.20273255405408211</v>
@@ -50875,7 +50903,7 @@
         <v>141</v>
       </c>
       <c r="B2004">
-        <v>6.6799999999999998E-2</v>
+        <v>0.47762</v>
       </c>
       <c r="C2004" t="s">
         <v>54</v>
@@ -50896,7 +50924,7 @@
         <v>2</v>
       </c>
       <c r="I2004">
-        <v>-2.7060521984395369</v>
+        <v>-0.7389398417336207</v>
       </c>
       <c r="J2004">
         <v>0.37096867236468872</v>
@@ -50913,7 +50941,7 @@
         <v>111</v>
       </c>
       <c r="B2005">
-        <v>0.89300000000000002</v>
+        <v>6.384950000000001</v>
       </c>
       <c r="C2005" t="s">
         <v>54</v>
@@ -50934,7 +50962,7 @@
         <v>2</v>
       </c>
       <c r="I2005">
-        <v>-0.113168698105638</v>
+        <v>1.8539436586002784</v>
       </c>
       <c r="J2005">
         <v>0.37096867236468872</v>
@@ -50951,7 +50979,7 @@
         <v>297</v>
       </c>
       <c r="B2006">
-        <v>2.22E-8</v>
+        <v>1.5873000000000002e-07</v>
       </c>
       <c r="C2006" t="s">
         <v>54</v>
@@ -50972,7 +51000,7 @@
         <v>2</v>
       </c>
       <c r="I2006">
-        <v>-17.623173548068181</v>
+        <v>-15.65606119136226</v>
       </c>
       <c r="J2006">
         <v>0.20273255405408211</v>
@@ -50989,7 +51017,7 @@
         <v>299</v>
       </c>
       <c r="B2007">
-        <v>1.38</v>
+        <v>9.866999999999999</v>
       </c>
       <c r="C2007" t="s">
         <v>54</v>
@@ -51010,7 +51038,7 @@
         <v>2</v>
       </c>
       <c r="I2007">
-        <v>0.32208349916911322</v>
+        <v>2.2891958558750294</v>
       </c>
       <c r="J2007">
         <v>4.7655089902162509E-2</v>
@@ -51027,7 +51055,7 @@
         <v>115</v>
       </c>
       <c r="B2008">
-        <v>2</v>
+        <v>14.3</v>
       </c>
       <c r="C2008" t="s">
         <v>54</v>
@@ -51048,7 +51076,7 @@
         <v>2</v>
       </c>
       <c r="I2008">
-        <v>0.69314718055994529</v>
+        <v>2.6602595372658615</v>
       </c>
       <c r="J2008">
         <v>4.7655089902162509E-2</v>
@@ -51065,7 +51093,7 @@
         <v>171</v>
       </c>
       <c r="B2009">
-        <v>35</v>
+        <v>250.25</v>
       </c>
       <c r="C2009" t="s">
         <v>54</v>
@@ -51086,7 +51114,7 @@
         <v>2</v>
       </c>
       <c r="I2009">
-        <v>3.555348061489414</v>
+        <v>5.52246041819533</v>
       </c>
       <c r="J2009">
         <v>0.1115717756571049</v>
@@ -51103,7 +51131,7 @@
         <v>254</v>
       </c>
       <c r="B2010">
-        <v>8</v>
+        <v>57.2</v>
       </c>
       <c r="C2010" t="s">
         <v>54</v>
@@ -51124,7 +51152,7 @@
         <v>2</v>
       </c>
       <c r="I2010">
-        <v>2.0794415416798362</v>
+        <v>4.046553898385752</v>
       </c>
       <c r="J2010">
         <v>4.7655089902162509E-2</v>
@@ -51148,8 +51176,15 @@
       <c r="A2013" t="s">
         <v>5</v>
       </c>
-      <c r="B2013" t="s">
-        <v>433</v>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="2014" spans="1:14" x14ac:dyDescent="0.2">
@@ -51246,7 +51281,7 @@
         <v>260</v>
       </c>
       <c r="B2021">
-        <v>1.1000000000000001E-3</v>
+        <v>0.007865</v>
       </c>
       <c r="C2021" t="s">
         <v>27</v>
@@ -51264,13 +51299,18 @@
         <v>2</v>
       </c>
       <c r="I2021">
-        <v>-6.812445099177812</v>
+        <v>-4.8453327424718955</v>
       </c>
       <c r="J2021">
         <v>4.7655089902162509E-2</v>
       </c>
-      <c r="L2021" t="s">
-        <v>261</v>
+      <c r="L2021" t="inlineStr">
+        <is>
+          <t>APPROVED EPR ENRICHMENT PRODUCT-REFERENCE RECONCILIATION, issue119, 2026-10-19. Simons and Bauer2012, DOI10.1177/0957650912440549, inherited EPR workbook enrichment/fuel-fabrication chain. IAEA separative-work definition https://www-pub.iaea.org/MTCD/publications/PDF/TE-771_Rev_1web.pdf . Original source coefficient basis not independently recovered.
+The enrichment activity is declared to produce1kg enriched4.8% uranium, but its fuel-fabrication consumer bought7.15kg per1kg heavy metal. The35kWh electricity and1.38kg uranium-hexafluoride input per former enrichment reference suggest a service basis, but the exact original SWU interpretation is not established. Do NOT treat7.15 as proven physical enriched-uranium consumption and do NOT divide total fuel-chain burdens by7.15.
+Make the existing declaration true by normalizing the enrichment service package to1kg enriched-U product: multiply EVERY nonproduction exchange (including biosphere, infrastructure, utilities, feed, transport and wastes) by7.15, and replace the fuel-fabrication input7.15 by1 at both FR/RER suppliers. Thus inherited total upstream burdens perkg fuel remain mathematically identical: 250.25kWh electricity and9.867 native referencekgUF6 perkg product, among other quantities. Production output remains1kg and identity remains unchanged so other code and links require no edits.
+This is a reference-basis correction, not an independently validated isotope-separation design or7.15SWU claim. Native uranium-bearing referencekg conventions must not be assumed to be physical kilograms of pureUF6 molecule; actual feed/product/tails assay, process losses and depleted-U fate remain source gaps. No new tails credit or generic uranium disposal is invented. Manufacturing fuel output remains heavy-metal basis, excluding oxygen and cladding. Existing UO2/MOX shares, reprocessing allocation, assembly materials and spent-fuel quantities are preserved. No native/runtime/share changes.</t>
+        </is>
       </c>
     </row>
     <row r="2022" spans="1:14" x14ac:dyDescent="0.2">
@@ -51278,7 +51318,7 @@
         <v>262</v>
       </c>
       <c r="B2022">
-        <v>3.8E-6</v>
+        <v>2.7170000000000002e-05</v>
       </c>
       <c r="C2022" t="s">
         <v>27</v>
@@ -51296,7 +51336,7 @@
         <v>2</v>
       </c>
       <c r="I2022">
-        <v>-12.480509491231929</v>
+        <v>-10.513397134526018</v>
       </c>
       <c r="J2022">
         <v>4.7655089902162509E-2</v>
@@ -51310,7 +51350,7 @@
         <v>263</v>
       </c>
       <c r="B2023">
-        <v>1.3E-6</v>
+        <v>9.295000000000002e-06</v>
       </c>
       <c r="C2023" t="s">
         <v>27</v>
@@ -51328,7 +51368,7 @@
         <v>2</v>
       </c>
       <c r="I2023">
-        <v>-13.553146293496781</v>
+        <v>-11.586033936790866</v>
       </c>
       <c r="J2023">
         <v>4.7655089902162509E-2</v>
@@ -51342,7 +51382,7 @@
         <v>264</v>
       </c>
       <c r="B2024">
-        <v>1.2999999999999999E-5</v>
+        <v>9.295e-05</v>
       </c>
       <c r="C2024" t="s">
         <v>27</v>
@@ -51360,7 +51400,7 @@
         <v>2</v>
       </c>
       <c r="I2024">
-        <v>-11.250561200502739</v>
+        <v>-9.28344884379682</v>
       </c>
       <c r="J2024">
         <v>0.13118213223374561</v>
@@ -51374,7 +51414,7 @@
         <v>266</v>
       </c>
       <c r="B2025">
-        <v>1.2999999999999999E-3</v>
+        <v>0.009295</v>
       </c>
       <c r="C2025" t="s">
         <v>27</v>
@@ -51392,7 +51432,7 @@
         <v>2</v>
       </c>
       <c r="I2025">
-        <v>-6.6453910145146464</v>
+        <v>-4.67827865780873</v>
       </c>
       <c r="J2025">
         <v>4.7655089902162509E-2</v>
@@ -51406,7 +51446,7 @@
         <v>204</v>
       </c>
       <c r="B2026">
-        <v>1.1E-4</v>
+        <v>0.0007865000000000001</v>
       </c>
       <c r="C2026" t="s">
         <v>27</v>
@@ -51424,7 +51464,7 @@
         <v>2</v>
       </c>
       <c r="I2026">
-        <v>-9.1150301921718579</v>
+        <v>-7.147917835465941</v>
       </c>
       <c r="J2026">
         <v>4.7655089902162509E-2</v>
@@ -51438,7 +51478,7 @@
         <v>32</v>
       </c>
       <c r="B2027">
-        <v>126</v>
+        <v>900.9000000000001</v>
       </c>
       <c r="C2027" t="s">
         <v>27</v>
@@ -51456,7 +51496,7 @@
         <v>2</v>
       </c>
       <c r="I2027">
-        <v>4.836281906951478</v>
+        <v>6.8033942636573945</v>
       </c>
       <c r="J2027">
         <v>4.7655089902162509E-2</v>
@@ -51470,7 +51510,7 @@
         <v>268</v>
       </c>
       <c r="B2028">
-        <v>6.0999999999999999E-5</v>
+        <v>0.00043615</v>
       </c>
       <c r="C2028" t="s">
         <v>27</v>
@@ -51488,7 +51528,7 @@
         <v>2</v>
       </c>
       <c r="I2028">
-        <v>-9.7046366937909632</v>
+        <v>-7.737524337085047</v>
       </c>
       <c r="J2028">
         <v>4.7655089902162509E-2</v>
@@ -51502,7 +51542,7 @@
         <v>269</v>
       </c>
       <c r="B2029">
-        <v>3.7E-8</v>
+        <v>2.6455e-07</v>
       </c>
       <c r="C2029" t="s">
         <v>27</v>
@@ -51520,7 +51560,7 @@
         <v>2</v>
       </c>
       <c r="I2029">
-        <v>-17.112347924302188</v>
+        <v>-15.14523556759627</v>
       </c>
       <c r="J2029">
         <v>4.7655089902162509E-2</v>
@@ -51534,7 +51574,7 @@
         <v>270</v>
       </c>
       <c r="B2030">
-        <v>2.5000000000000001E-3</v>
+        <v>0.017875000000000002</v>
       </c>
       <c r="C2030" t="s">
         <v>27</v>
@@ -51552,7 +51592,7 @@
         <v>2</v>
       </c>
       <c r="I2030">
-        <v>-5.9914645471079817</v>
+        <v>-4.024352190402065</v>
       </c>
       <c r="J2030">
         <v>4.7655089902162509E-2</v>
@@ -51566,7 +51606,7 @@
         <v>271</v>
       </c>
       <c r="B2031">
-        <v>3.4000000000000002E-4</v>
+        <v>0.0024310000000000004</v>
       </c>
       <c r="C2031" t="s">
         <v>27</v>
@@ -51584,7 +51624,7 @@
         <v>2</v>
       </c>
       <c r="I2031">
-        <v>-7.9865649403540671</v>
+        <v>-6.0194525836481505</v>
       </c>
       <c r="J2031">
         <v>4.7655089902162509E-2</v>
@@ -51598,7 +51638,7 @@
         <v>272</v>
       </c>
       <c r="B2032">
-        <v>2.2000000000000001E-6</v>
+        <v>1.573e-05</v>
       </c>
       <c r="C2032" t="s">
         <v>27</v>
@@ -51616,7 +51656,7 @@
         <v>2</v>
       </c>
       <c r="I2032">
-        <v>-13.027053197600001</v>
+        <v>-11.059940840894088</v>
       </c>
       <c r="J2032">
         <v>0.20273255405408211</v>
@@ -51630,7 +51670,7 @@
         <v>272</v>
       </c>
       <c r="B2033">
-        <v>3.0999999999999999E-3</v>
+        <v>0.022165</v>
       </c>
       <c r="C2033" t="s">
         <v>27</v>
@@ -51648,7 +51688,7 @@
         <v>2</v>
       </c>
       <c r="I2033">
-        <v>-5.7763531674910356</v>
+        <v>-3.8092408107851203</v>
       </c>
       <c r="J2033">
         <v>4.7655089902162509E-2</v>
@@ -51662,7 +51702,7 @@
         <v>257</v>
       </c>
       <c r="B2034">
-        <v>3.1000000000000001E-5</v>
+        <v>0.00022165000000000002</v>
       </c>
       <c r="C2034" t="s">
         <v>27</v>
@@ -51680,7 +51720,7 @@
         <v>2</v>
       </c>
       <c r="I2034">
-        <v>-10.38152335347913</v>
+        <v>-8.414410996773212</v>
       </c>
       <c r="J2034">
         <v>4.7655089902162509E-2</v>
@@ -51694,7 +51734,7 @@
         <v>257</v>
       </c>
       <c r="B2035">
-        <v>8.1999999999999994E-6</v>
+        <v>5.863e-05</v>
       </c>
       <c r="C2035" t="s">
         <v>27</v>
@@ -51712,7 +51752,7 @@
         <v>2</v>
       </c>
       <c r="I2035">
-        <v>-11.71137640369407</v>
+        <v>-9.74426404698815</v>
       </c>
       <c r="J2035">
         <v>4.7655089902162509E-2</v>
@@ -51726,7 +51766,7 @@
         <v>274</v>
       </c>
       <c r="B2036">
-        <v>3.8000000000000002E-5</v>
+        <v>0.00027170000000000004</v>
       </c>
       <c r="C2036" t="s">
         <v>27</v>
@@ -51744,7 +51784,7 @@
         <v>2</v>
       </c>
       <c r="I2036">
-        <v>-10.17792439823789</v>
+        <v>-8.210812041531971</v>
       </c>
       <c r="J2036">
         <v>4.7655089902162509E-2</v>
@@ -51790,7 +51830,7 @@
         <v>57</v>
       </c>
       <c r="B2038">
-        <v>2.5000000000000001E-5</v>
+        <v>0.00017875</v>
       </c>
       <c r="C2038" t="s">
         <v>54</v>
@@ -51811,7 +51851,7 @@
         <v>2</v>
       </c>
       <c r="I2038">
-        <v>-10.596634733096071</v>
+        <v>-8.629522376390158</v>
       </c>
       <c r="J2038">
         <v>4.7655089902162509E-2</v>
@@ -51828,7 +51868,7 @@
         <v>134</v>
       </c>
       <c r="B2039">
-        <v>0.05</v>
+        <v>0.35750000000000004</v>
       </c>
       <c r="C2039" t="s">
         <v>54</v>
@@ -51849,7 +51889,7 @@
         <v>2</v>
       </c>
       <c r="I2039">
-        <v>-2.9957322735539909</v>
+        <v>-1.0286199168480745</v>
       </c>
       <c r="J2039">
         <v>0.3465735902799727</v>
@@ -51866,7 +51906,7 @@
         <v>61</v>
       </c>
       <c r="B2040">
-        <v>1.8E-3</v>
+        <v>0.01287</v>
       </c>
       <c r="C2040" t="s">
         <v>54</v>
@@ -51887,7 +51927,7 @@
         <v>2</v>
       </c>
       <c r="I2040">
-        <v>-6.3199686140800182</v>
+        <v>-4.352856257374102</v>
       </c>
       <c r="J2040">
         <v>4.7655089902162509E-2</v>
@@ -51904,7 +51944,7 @@
         <v>64</v>
       </c>
       <c r="B2041">
-        <v>2.3999999999999998E-3</v>
+        <v>0.017159999999999998</v>
       </c>
       <c r="C2041" t="s">
         <v>54</v>
@@ -51925,7 +51965,7 @@
         <v>2</v>
       </c>
       <c r="I2041">
-        <v>-6.0322865416282374</v>
+        <v>-4.065174184922321</v>
       </c>
       <c r="J2041">
         <v>4.7655089902162509E-2</v>
@@ -51942,7 +51982,7 @@
         <v>276</v>
       </c>
       <c r="B2042">
-        <v>1.8E-3</v>
+        <v>0.01287</v>
       </c>
       <c r="C2042" t="s">
         <v>54</v>
@@ -51963,7 +52003,7 @@
         <v>2</v>
       </c>
       <c r="I2042">
-        <v>-6.3199686140800182</v>
+        <v>-4.352856257374102</v>
       </c>
       <c r="J2042">
         <v>0.3465735902799727</v>
@@ -51980,7 +52020,7 @@
         <v>76</v>
       </c>
       <c r="B2043">
-        <v>3.1099999999999999E-2</v>
+        <v>0.222365</v>
       </c>
       <c r="C2043" t="s">
         <v>54</v>
@@ -52001,7 +52041,7 @@
         <v>2</v>
       </c>
       <c r="I2043">
-        <v>-3.4705474597969488</v>
+        <v>-1.5034351030910322</v>
       </c>
       <c r="J2043">
         <v>4.7655089902162509E-2</v>
@@ -52018,7 +52058,7 @@
         <v>80</v>
       </c>
       <c r="B2044">
-        <v>8.1999999999999998E-4</v>
+        <v>0.005863</v>
       </c>
       <c r="C2044" t="s">
         <v>54</v>
@@ -52039,7 +52079,7 @@
         <v>2</v>
       </c>
       <c r="I2044">
-        <v>-7.1062062177059753</v>
+        <v>-5.139093861000059</v>
       </c>
       <c r="J2044">
         <v>4.7655089902162509E-2</v>
@@ -52056,7 +52096,7 @@
         <v>83</v>
       </c>
       <c r="B2045">
-        <v>2.9E-4</v>
+        <v>0.0020735000000000003</v>
       </c>
       <c r="C2045" t="s">
         <v>54</v>
@@ -52077,7 +52117,7 @@
         <v>2</v>
       </c>
       <c r="I2045">
-        <v>-8.145629634983754</v>
+        <v>-6.178517278277838</v>
       </c>
       <c r="J2045">
         <v>0.3465735902799727</v>
@@ -52094,7 +52134,7 @@
         <v>85</v>
       </c>
       <c r="B2046">
-        <v>0.6</v>
+        <v>4.29</v>
       </c>
       <c r="C2046" t="s">
         <v>54</v>
@@ -52115,7 +52155,7 @@
         <v>2</v>
       </c>
       <c r="I2046">
-        <v>-0.51082562376599072</v>
+        <v>1.4562867329399256</v>
       </c>
       <c r="J2046">
         <v>4.7655089902162509E-2</v>
@@ -52132,7 +52172,7 @@
         <v>169</v>
       </c>
       <c r="B2047">
-        <v>35</v>
+        <v>250.25</v>
       </c>
       <c r="C2047" t="s">
         <v>54</v>
@@ -52153,7 +52193,7 @@
         <v>2</v>
       </c>
       <c r="I2047">
-        <v>3.555348061489414</v>
+        <v>5.52246041819533</v>
       </c>
       <c r="J2047">
         <v>0.1115717756571049</v>
@@ -52170,7 +52210,7 @@
         <v>278</v>
       </c>
       <c r="B2048">
-        <v>2.0000000000000001E-4</v>
+        <v>0.00143</v>
       </c>
       <c r="C2048" t="s">
         <v>54</v>
@@ -52191,7 +52231,7 @@
         <v>2</v>
       </c>
       <c r="I2048">
-        <v>-8.5171931914162382</v>
+        <v>-6.550080834710321</v>
       </c>
       <c r="J2048">
         <v>4.7655089902162509E-2</v>
@@ -52208,7 +52248,7 @@
         <v>280</v>
       </c>
       <c r="B2049">
-        <v>6.8000000000000005E-4</v>
+        <v>0.004862000000000001</v>
       </c>
       <c r="C2049" t="s">
         <v>54</v>
@@ -52229,7 +52269,7 @@
         <v>2</v>
       </c>
       <c r="I2049">
-        <v>-7.2934177597941217</v>
+        <v>-5.326305403088205</v>
       </c>
       <c r="J2049">
         <v>4.7655089902162509E-2</v>
@@ -52246,7 +52286,7 @@
         <v>90</v>
       </c>
       <c r="B2050">
-        <v>1.1E-5</v>
+        <v>7.865e-05</v>
       </c>
       <c r="C2050" t="s">
         <v>54</v>
@@ -52267,7 +52307,7 @@
         <v>2</v>
       </c>
       <c r="I2050">
-        <v>-11.417615285165899</v>
+        <v>-9.450502928459986</v>
       </c>
       <c r="J2050">
         <v>4.7655089902162509E-2</v>
@@ -52284,7 +52324,7 @@
         <v>228</v>
       </c>
       <c r="B2051">
-        <v>-3.0000000000000001E-6</v>
+        <v>-2.1450000000000003e-05</v>
       </c>
       <c r="C2051" t="s">
         <v>54</v>
@@ -52305,7 +52345,7 @@
         <v>2</v>
       </c>
       <c r="I2051">
-        <v>-12.716898269296159</v>
+        <v>-10.749785912590248</v>
       </c>
       <c r="J2051">
         <v>4.7655089902162509E-2</v>
@@ -52325,7 +52365,7 @@
         <v>92</v>
       </c>
       <c r="B2052">
-        <v>9.1999999999999998E-3</v>
+        <v>0.06578</v>
       </c>
       <c r="C2052" t="s">
         <v>54</v>
@@ -52346,7 +52386,7 @@
         <v>2</v>
       </c>
       <c r="I2052">
-        <v>-4.6885517949271422</v>
+        <v>-2.721439438221226</v>
       </c>
       <c r="J2052">
         <v>4.7655089902162509E-2</v>
@@ -52363,7 +52403,7 @@
         <v>282</v>
       </c>
       <c r="B2053">
-        <v>3.2000000000000003E-4</v>
+        <v>0.002288</v>
       </c>
       <c r="C2053" t="s">
         <v>54</v>
@@ -52384,7 +52424,7 @@
         <v>2</v>
       </c>
       <c r="I2053">
-        <v>-8.0471895621705016</v>
+        <v>-6.080077205464586</v>
       </c>
       <c r="J2053">
         <v>4.7655089902162509E-2</v>
@@ -52401,7 +52441,7 @@
         <v>284</v>
       </c>
       <c r="B2054">
-        <v>-0.23499999999999999</v>
+        <v>-1.68025</v>
       </c>
       <c r="C2054" t="s">
         <v>54</v>
@@ -52422,7 +52462,7 @@
         <v>2</v>
       </c>
       <c r="I2054">
-        <v>-1.4481697648379781</v>
+        <v>0.5189425918679382</v>
       </c>
       <c r="J2054">
         <v>4.7655089902162509E-2</v>
@@ -52442,7 +52482,7 @@
         <v>286</v>
       </c>
       <c r="B2055">
-        <v>1.5E-3</v>
+        <v>0.010725</v>
       </c>
       <c r="C2055" t="s">
         <v>54</v>
@@ -52463,7 +52503,7 @@
         <v>2</v>
       </c>
       <c r="I2055">
-        <v>-6.5022901708739722</v>
+        <v>-4.5351778141680565</v>
       </c>
       <c r="J2055">
         <v>4.7655089902162509E-2</v>
@@ -52480,7 +52520,7 @@
         <v>96</v>
       </c>
       <c r="B2056">
-        <v>3.8999999999999999E-4</v>
+        <v>0.0027885</v>
       </c>
       <c r="C2056" t="s">
         <v>54</v>
@@ -52501,7 +52541,7 @@
         <v>2</v>
       </c>
       <c r="I2056">
-        <v>-7.8493638188405823</v>
+        <v>-5.882251462134666</v>
       </c>
       <c r="J2056">
         <v>4.7655089902162509E-2</v>
@@ -52518,7 +52558,7 @@
         <v>100</v>
       </c>
       <c r="B2057">
-        <v>3.6000000000000001E-5</v>
+        <v>0.0002574</v>
       </c>
       <c r="C2057" t="s">
         <v>54</v>
@@ -52539,7 +52579,7 @@
         <v>2</v>
       </c>
       <c r="I2057">
-        <v>-10.231991619508159</v>
+        <v>-8.264879262802248</v>
       </c>
       <c r="J2057">
         <v>4.7655089902162509E-2</v>
@@ -52556,7 +52596,7 @@
         <v>289</v>
       </c>
       <c r="B2058">
-        <v>1.2E-4</v>
+        <v>0.000858</v>
       </c>
       <c r="C2058" t="s">
         <v>54</v>
@@ -52577,7 +52617,7 @@
         <v>2</v>
       </c>
       <c r="I2058">
-        <v>-9.0280188151822287</v>
+        <v>-7.060906458476312</v>
       </c>
       <c r="J2058">
         <v>4.7655089902162509E-2</v>
@@ -52594,7 +52634,7 @@
         <v>148</v>
       </c>
       <c r="B2059">
-        <v>8.7000000000000001E-4</v>
+        <v>0.0062205</v>
       </c>
       <c r="C2059" t="s">
         <v>54</v>
@@ -52615,7 +52655,7 @@
         <v>2</v>
       </c>
       <c r="I2059">
-        <v>-7.0470173463156449</v>
+        <v>-5.079904989609728</v>
       </c>
       <c r="J2059">
         <v>4.7655089902162509E-2</v>
@@ -52632,7 +52672,7 @@
         <v>291</v>
       </c>
       <c r="B2060">
-        <v>8.8000000000000003E-4</v>
+        <v>0.006292000000000001</v>
       </c>
       <c r="C2060" t="s">
         <v>54</v>
@@ -52653,7 +52693,7 @@
         <v>2</v>
       </c>
       <c r="I2060">
-        <v>-7.0355886504920218</v>
+        <v>-5.068476293786105</v>
       </c>
       <c r="J2060">
         <v>4.7655089902162509E-2</v>
@@ -52670,7 +52710,7 @@
         <v>293</v>
       </c>
       <c r="B2061">
-        <v>2.8E-3</v>
+        <v>0.02002</v>
       </c>
       <c r="C2061" t="s">
         <v>54</v>
@@ -52691,7 +52731,7 @@
         <v>2</v>
       </c>
       <c r="I2061">
-        <v>-5.8781358618009776</v>
+        <v>-3.9110235050950624</v>
       </c>
       <c r="J2061">
         <v>4.7655089902162509E-2</v>
@@ -52708,7 +52748,7 @@
         <v>295</v>
       </c>
       <c r="B2062">
-        <v>5.8000000000000003E-2</v>
+        <v>0.41470000000000007</v>
       </c>
       <c r="C2062" t="s">
         <v>54</v>
@@ -52729,7 +52769,7 @@
         <v>2</v>
       </c>
       <c r="I2062">
-        <v>-2.8473122684357182</v>
+        <v>-0.8801999117298013</v>
       </c>
       <c r="J2062">
         <v>4.7655089902162509E-2</v>
@@ -52746,7 +52786,7 @@
         <v>108</v>
       </c>
       <c r="B2063">
-        <v>0.15</v>
+        <v>1.0725</v>
       </c>
       <c r="C2063" t="s">
         <v>54</v>
@@ -52767,7 +52807,7 @@
         <v>2</v>
       </c>
       <c r="I2063">
-        <v>-1.8971199848858811</v>
+        <v>0.069992371820035</v>
       </c>
       <c r="J2063">
         <v>0.20273255405408211</v>
@@ -52784,7 +52824,7 @@
         <v>141</v>
       </c>
       <c r="B2064">
-        <v>6.6799999999999998E-2</v>
+        <v>0.47762</v>
       </c>
       <c r="C2064" t="s">
         <v>54</v>
@@ -52805,7 +52845,7 @@
         <v>2</v>
       </c>
       <c r="I2064">
-        <v>-2.7060521984395369</v>
+        <v>-0.7389398417336207</v>
       </c>
       <c r="J2064">
         <v>0.37096867236468872</v>
@@ -52822,7 +52862,7 @@
         <v>111</v>
       </c>
       <c r="B2065">
-        <v>0.89300000000000002</v>
+        <v>6.384950000000001</v>
       </c>
       <c r="C2065" t="s">
         <v>54</v>
@@ -52843,7 +52883,7 @@
         <v>2</v>
       </c>
       <c r="I2065">
-        <v>-0.113168698105638</v>
+        <v>1.8539436586002784</v>
       </c>
       <c r="J2065">
         <v>0.37096867236468872</v>
@@ -52860,7 +52900,7 @@
         <v>297</v>
       </c>
       <c r="B2066">
-        <v>2.22E-8</v>
+        <v>1.5873000000000002e-07</v>
       </c>
       <c r="C2066" t="s">
         <v>54</v>
@@ -52881,7 +52921,7 @@
         <v>2</v>
       </c>
       <c r="I2066">
-        <v>-17.623173548068181</v>
+        <v>-15.65606119136226</v>
       </c>
       <c r="J2066">
         <v>0.20273255405408211</v>
@@ -52898,7 +52938,7 @@
         <v>299</v>
       </c>
       <c r="B2067">
-        <v>1.38</v>
+        <v>9.866999999999999</v>
       </c>
       <c r="C2067" t="s">
         <v>54</v>
@@ -52919,7 +52959,7 @@
         <v>2</v>
       </c>
       <c r="I2067">
-        <v>0.32208349916911322</v>
+        <v>2.2891958558750294</v>
       </c>
       <c r="J2067">
         <v>4.7655089902162509E-2</v>
@@ -52936,7 +52976,7 @@
         <v>115</v>
       </c>
       <c r="B2068">
-        <v>2</v>
+        <v>14.3</v>
       </c>
       <c r="C2068" t="s">
         <v>54</v>
@@ -52957,7 +52997,7 @@
         <v>2</v>
       </c>
       <c r="I2068">
-        <v>0.69314718055994529</v>
+        <v>2.6602595372658615</v>
       </c>
       <c r="J2068">
         <v>4.7655089902162509E-2</v>
@@ -52974,7 +53014,7 @@
         <v>254</v>
       </c>
       <c r="B2069">
-        <v>8</v>
+        <v>57.2</v>
       </c>
       <c r="C2069" t="s">
         <v>54</v>
@@ -52995,7 +53035,7 @@
         <v>2</v>
       </c>
       <c r="I2069">
-        <v>2.0794415416798362</v>
+        <v>4.046553898385752</v>
       </c>
       <c r="J2069">
         <v>4.7655089902162509E-2</v>

--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -45775,8 +45775,15 @@
       <c r="A1826" t="s">
         <v>5</v>
       </c>
-      <c r="B1826" t="s">
-        <v>433</v>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1827" spans="1:14" x14ac:dyDescent="0.2">
@@ -45893,6 +45900,14 @@
       <c r="J1834">
         <v>100</v>
       </c>
+      <c r="K1834" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.</t>
+        </is>
+      </c>
       <c r="M1834" t="s">
         <v>361</v>
       </c>
@@ -45963,6 +45978,14 @@
       <c r="I1836">
         <v>5300000</v>
       </c>
+      <c r="K1836" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.</t>
+        </is>
+      </c>
       <c r="L1836" t="s">
         <v>155</v>
       </c>
@@ -46061,8 +46084,15 @@
       <c r="A1841" t="s">
         <v>5</v>
       </c>
-      <c r="B1841" t="s">
-        <v>433</v>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Simons A, Bauer C. Life cycle assessment of the Evolutionary Power Reactor (EPR) and the influence of different fuel cycle strategies. Proceedings of the Institution of Mechanical Engineers, Part A: Journal of Power and Energy. 2012;226(3):427-444. doi:10.1177/0957650912440549</t>
+        </is>
       </c>
     </row>
     <row r="1842" spans="1:14" x14ac:dyDescent="0.2">
@@ -46179,6 +46209,14 @@
       <c r="J1849">
         <v>100</v>
       </c>
+      <c r="K1849" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.</t>
+        </is>
+      </c>
       <c r="M1849" t="s">
         <v>361</v>
       </c>
@@ -46248,6 +46286,14 @@
       </c>
       <c r="I1851">
         <v>5300000</v>
+      </c>
+      <c r="K1851" t="inlineStr">
+        <is>
+          <t>APPROVED EPR TURBINE ALLOY AUDIT, issue121, 2026-10-19. Japan Steel Works manufacturer examples distinguish LP turbine rotor Super Clean3.5%NiCrMoV steel and IP rotor12%Cr steel: https://www.jsw.co.jp/en/product/business/me_1000_en_03.html . These examples are not a component-mass BOM for the EPR turbine. Original source Simons/Bauer2012 DOI10.1177/0957650912440549.
+UNRESOLVED MATERIAL SPECIFICATION: each CH/RER turbine reference supplies5300000kg as18/8 stainless steel. This is a bulk-alloy proxy, not evidence every rotor, casing and blade is that grade. Interpreting18/8 nominally would embed424000kgNi and954000kgCr perplant; these are nominal alloy-content illustrations, NOT independently calculated upstream refined-metal demand, recovery or a sourced replacement BOM.
+Manufacturer examples establish different alloy families for different components but do not establish EPR component masses or how much of5300tonnes belongs to each. Consequently no arbitrary split or wholesale replacement by carbon/low-alloy steel is justified. Retain all numerical exchanges pending a matched EPR turbine material schedule. Required data: casing/rotor/blade masses and grades, inclusion of auxiliaries, manufacturing yields and corresponding retirement boundary. Evaluate source-consistent component mixtures as sensitivity after these data are recovered; do not present current Ni/Cr quantities as validated turbine intensities.
+This targeted workbook documentation commit records an open correction, not a numerical resolution. It prevents a source gap from being silently relabelled as correct. No native/runtime/source mass/share edits.</t>
+        </is>
       </c>
       <c r="L1851" t="s">
         <v>155</v>

--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -25676,7 +25676,7 @@
     <row r="990" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A990" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="B990">
@@ -25725,12 +25725,12 @@
       </c>
       <c r="N990" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="O990" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="P990" t="s">
@@ -27279,7 +27279,7 @@
     <row r="1038" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1038" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1038">
@@ -27328,12 +27328,12 @@
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="O1038" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="P1038" t="s">
@@ -47491,7 +47491,7 @@
     <row r="1894" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1894" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1894">
@@ -47537,7 +47537,7 @@
       </c>
       <c r="N1894" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -48964,7 +48964,7 @@
     <row r="1943" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1943" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1943">
@@ -49010,7 +49010,7 @@
       </c>
       <c r="N1943" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -54412,7 +54412,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
         </is>
       </c>
     </row>
@@ -54446,7 +54446,7 @@
       </c>
       <c r="B2132" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
     </row>
@@ -54482,7 +54482,8 @@
       </c>
       <c r="B2135" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: zirconium cladding metal, oxide-to-Kroll engineering reference. Former reference product: zirconium cladding metal, oxide-to-Kroll engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -54548,7 +54549,7 @@
     <row r="2138">
       <c r="A2138" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
         </is>
       </c>
       <c r="B2138">
@@ -54571,12 +54572,12 @@
       </c>
       <c r="G2138" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
       <c r="I2138" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
     </row>
@@ -54903,7 +54904,7 @@
       </c>
       <c r="B2150" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
     </row>
@@ -54937,7 +54938,7 @@
       </c>
       <c r="B2153" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
@@ -54973,7 +54974,8 @@
       </c>
       <c r="B2156" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: niobium metal equivalent, ferroniobium feed and separation reference. Former reference product: niobium metal equivalent, ferroniobium feed and separation reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -55039,7 +55041,7 @@
     <row r="2159">
       <c r="A2159" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
       <c r="B2159">
@@ -55062,12 +55064,12 @@
       </c>
       <c r="G2159" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
       <c r="I2159" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
@@ -55184,7 +55186,7 @@
       </c>
       <c r="B2165" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
         </is>
       </c>
     </row>
@@ -55218,7 +55220,7 @@
       </c>
       <c r="B2168" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
@@ -55254,7 +55256,8 @@
       </c>
       <c r="B2171" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR M5-type zirconium cladding, nominal alloy reference. Former reference product: EPR M5-type zirconium cladding, nominal alloy reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -55320,7 +55323,7 @@
     <row r="2174">
       <c r="A2174" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
         </is>
       </c>
       <c r="B2174">
@@ -55343,19 +55346,19 @@
       </c>
       <c r="G2174" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
       <c r="I2174" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
     <row r="2175">
       <c r="A2175" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
         </is>
       </c>
       <c r="B2175">
@@ -55378,19 +55381,19 @@
       </c>
       <c r="G2175" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
       <c r="I2175" t="inlineStr">
         <is>
-          <t>zirconium cladding metal, oxide-to-Kroll engineering reference</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
     </row>
     <row r="2176">
       <c r="A2176" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
       <c r="B2176">
@@ -55413,12 +55416,12 @@
       </c>
       <c r="G2176" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
       <c r="I2176" t="inlineStr">
         <is>
-          <t>niobium metal equivalent, ferroniobium feed and separation reference</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
@@ -55605,7 +55608,7 @@
       </c>
       <c r="B2184" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
@@ -55639,7 +55642,7 @@
       </c>
       <c r="B2187" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
@@ -55675,7 +55678,8 @@
       </c>
       <c r="B2190" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR Inconel718-type spring alloy, nominal reference. Former reference product: EPR Inconel718-type spring alloy, nominal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -55741,7 +55745,7 @@
     <row r="2193">
       <c r="A2193" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
         </is>
       </c>
       <c r="B2193">
@@ -55764,12 +55768,12 @@
       </c>
       <c r="G2193" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
       <c r="I2193" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
@@ -56166,7 +56170,7 @@
       </c>
       <c r="B2207" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -56200,7 +56204,7 @@
       </c>
       <c r="B2210" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -56236,7 +56240,8 @@
       </c>
       <c r="B2213" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Former reference product: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -56302,7 +56307,7 @@
     <row r="2216">
       <c r="A2216" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="B2216">
@@ -56325,19 +56330,19 @@
       </c>
       <c r="G2216" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="I2216" t="inlineStr">
         <is>
-          <t>EPR fuel-assembly nonfuel materials, per kg heavy-metal reference</t>
+          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
     <row r="2217">
       <c r="A2217" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
         </is>
       </c>
       <c r="B2217">
@@ -56360,19 +56365,19 @@
       </c>
       <c r="G2217" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
       <c r="I2217" t="inlineStr">
         <is>
-          <t>EPR M5-type zirconium cladding, nominal alloy reference</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
     <row r="2218">
       <c r="A2218" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
         </is>
       </c>
       <c r="B2218">
@@ -56395,12 +56400,12 @@
       </c>
       <c r="G2218" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
       <c r="I2218" t="inlineStr">
         <is>
-          <t>EPR Inconel718-type spring alloy, nominal reference</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -25680,7 +25680,7 @@
         </is>
       </c>
       <c r="B990">
-        <v>1</v>
+        <v>0.344218009478673</v>
       </c>
       <c r="C990" t="s">
         <v>54</v>
@@ -25692,7 +25692,7 @@
       </c>
       <c r="E990" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F990" t="s">
@@ -25705,14 +25705,15 @@
         <v>2</v>
       </c>
       <c r="I990">
-        <v>0.0</v>
+        <v>-1.0664800738579896</v>
       </c>
       <c r="J990">
         <v>4.7655089902162509E-2</v>
       </c>
       <c r="L990" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -25725,12 +25726,12 @@
       </c>
       <c r="N990" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="O990" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="P990" t="s">
@@ -27283,7 +27284,7 @@
         </is>
       </c>
       <c r="B1038">
-        <v>1</v>
+        <v>0.344218009478673</v>
       </c>
       <c r="C1038" t="s">
         <v>54</v>
@@ -27295,7 +27296,7 @@
       </c>
       <c r="E1038" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F1038" t="s">
@@ -27308,14 +27309,15 @@
         <v>2</v>
       </c>
       <c r="I1038">
-        <v>0.0</v>
+        <v>-1.0664800738579896</v>
       </c>
       <c r="J1038">
         <v>4.7655089902162509E-2</v>
       </c>
       <c r="L1038" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -27328,12 +27330,12 @@
       </c>
       <c r="N1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="O1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="P1038" t="s">
@@ -47495,7 +47497,7 @@
         </is>
       </c>
       <c r="B1894">
-        <v>1</v>
+        <v>0.344218009478673</v>
       </c>
       <c r="C1894" t="s">
         <v>54</v>
@@ -47507,7 +47509,7 @@
       </c>
       <c r="E1894" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F1894" t="s">
@@ -47520,14 +47522,15 @@
         <v>2</v>
       </c>
       <c r="I1894">
-        <v>0.0</v>
+        <v>-1.0664800738579896</v>
       </c>
       <c r="J1894">
         <v>4.7655089902162509E-2</v>
       </c>
       <c r="L1894" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -47537,7 +47540,7 @@
       </c>
       <c r="N1894" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -48968,7 +48971,7 @@
         </is>
       </c>
       <c r="B1943">
-        <v>1</v>
+        <v>0.344218009478673</v>
       </c>
       <c r="C1943" t="s">
         <v>54</v>
@@ -48980,7 +48983,7 @@
       </c>
       <c r="E1943" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F1943" t="s">
@@ -48993,14 +48996,15 @@
         <v>2</v>
       </c>
       <c r="I1943">
-        <v>0.0</v>
+        <v>-1.0664800738579896</v>
       </c>
       <c r="J1943">
         <v>4.7655089902162509E-2</v>
       </c>
       <c r="L1943" t="inlineStr">
         <is>
-          <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
 M5-type nominal fractions {'Nb': 0.01, 'Fe': 0.00035, 'O': 0.00125, 'Zr': 0.9884} are an engineering alloy reference: 1%Nb from source; 0.035%Fe and0.125%O are explicit trace-alloy selections, not a measured EPR heat. Source p24 approximate98.5%Zr is rounded, not an exact closing recipe. Nuclear-grade zirconium sponge is supplied at the retained Zr fraction; actual tube manufacture/purity losses remain gaps. Nb metal is unavailable in native inventory: supply 1/0.66kg ferroniobium perkgNb equivalent, assign its 0.34/0.66kgFe to generic inert reject, and allow5kWh/kgNb separation. This is a transparent upstream feed/energy proxy, NOT a validated chemical separation or nuclear-purity route; actual reagents, yield, impurities and Fe fate need data (2-20kWh/kgNb sensitivity). It prevents silently omitting Nb or retaining ferroniobium iron in a low-Fe M5 alloy. No recovery credit.
@@ -49010,7 +49014,7 @@
       </c>
       <c r="N1943" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -56204,7 +56208,7 @@
       </c>
       <c r="B2210" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -56216,7 +56220,7 @@
       </c>
       <c r="B2211" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
@@ -56240,7 +56244,8 @@
       </c>
       <c r="B2213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Former reference product: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+          <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
+Nomenclature revision, 2026-10-19. Former activity name: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Former reference product: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
 The same hardware perkgHM is adopted for the EPR MOX variant as an explicit common-geometry assumption; MOX-specific assembly design and pellet density differences remain unresolved. Preserve fuel enrichment/mix, burnup, operating energy and existing spent-fuel treatment. Do not introduce MOX reprocessing/enrichment burdens already allocated elsewhere.
@@ -56320,7 +56325,7 @@
       </c>
       <c r="D2216" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t xml:space="preserve">kilogram</t>
         </is>
       </c>
       <c r="F2216" t="inlineStr">
@@ -56330,12 +56335,12 @@
       </c>
       <c r="G2216" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
       <c r="I2216" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
@@ -56346,7 +56351,7 @@
         </is>
       </c>
       <c r="B2217">
-        <v>0.30714691943127964</v>
+        <v>0.8923034558722291</v>
       </c>
       <c r="C2217" t="inlineStr">
         <is>
@@ -56381,7 +56386,7 @@
         </is>
       </c>
       <c r="B2218">
-        <v>0.008265402843601895</v>
+        <v>0.024012116205424754</v>
       </c>
       <c r="C2218" t="inlineStr">
         <is>
@@ -56416,7 +56421,7 @@
         </is>
       </c>
       <c r="B2219">
-        <v>0.02767772511848341</v>
+        <v>0.08040754509155995</v>
       </c>
       <c r="C2219" t="inlineStr">
         <is>
@@ -56451,7 +56456,7 @@
         </is>
       </c>
       <c r="B2220">
-        <v>0.0011279620853080568</v>
+        <v>0.003276882830786176</v>
       </c>
       <c r="C2220" t="inlineStr">
         <is>

--- a/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_EPR.xlsx
@@ -1694,7 +1694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2220"/>
+  <dimension ref="A1:P2225"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.83203125" customWidth="1"/>
@@ -25676,7 +25676,7 @@
     <row r="990" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A990" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
       <c r="B990">
@@ -27280,7 +27280,7 @@
     <row r="1038" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1038" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1038">
@@ -47493,7 +47493,7 @@
     <row r="1894" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1894" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1894">
@@ -48967,7 +48967,7 @@
     <row r="1943" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1943" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
       <c r="B1943">
@@ -54416,7 +54416,7 @@
       </c>
       <c r="B2129" t="inlineStr">
         <is>
-          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
+          <t xml:space="preserve">zirconium metal production, cladding, kroll process</t>
         </is>
       </c>
     </row>
@@ -54499,100 +54499,77 @@
     <row r="2136">
       <c r="A2136" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B2136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="2137">
       <c r="A2137" t="inlineStr">
         <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2137" t="inlineStr">
+      <c r="B2138" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C2137" t="inlineStr">
+      <c r="C2138" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D2137" t="inlineStr">
+      <c r="D2138" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2137" t="inlineStr">
+      <c r="E2138" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F2137" t="inlineStr">
+      <c r="F2138" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2137" t="inlineStr">
+      <c r="G2138" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H2137" t="inlineStr">
+      <c r="H2138" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I2137" t="inlineStr">
+      <c r="I2138" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="2138">
-      <c r="A2138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
-        </is>
-      </c>
-      <c r="B2138">
-        <v>1</v>
-      </c>
-      <c r="C2138" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2138" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2138" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G2138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
-        </is>
-      </c>
-      <c r="I2138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
-        </is>
-      </c>
-    </row>
     <row r="2139">
       <c r="A2139" t="inlineStr">
         <is>
-          <t>market for zirconium oxide</t>
+          <t xml:space="preserve">zirconium metal production, cladding, kroll process</t>
         </is>
       </c>
       <c r="B2139">
-        <v>1.4218557443332087</v>
+        <v>1</v>
       </c>
       <c r="C2139" t="inlineStr">
         <is>
@@ -54606,28 +54583,28 @@
       </c>
       <c r="F2139" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G2139" t="inlineStr">
         <is>
-          <t>zirconium oxide</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
       <c r="I2139" t="inlineStr">
         <is>
-          <t>zirconium oxide</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
     </row>
     <row r="2140">
       <c r="A2140" t="inlineStr">
         <is>
-          <t>market for graphite</t>
+          <t>market for zirconium oxide</t>
         </is>
       </c>
       <c r="B2140">
-        <v>0.27718928998370695</v>
+        <v>1.4218557443332087</v>
       </c>
       <c r="C2140" t="inlineStr">
         <is>
@@ -54646,27 +54623,27 @@
       </c>
       <c r="G2140" t="inlineStr">
         <is>
-          <t>graphite</t>
+          <t>zirconium oxide</t>
         </is>
       </c>
       <c r="I2140" t="inlineStr">
         <is>
-          <t>graphite</t>
+          <t>zirconium oxide</t>
         </is>
       </c>
     </row>
     <row r="2141">
       <c r="A2141" t="inlineStr">
         <is>
-          <t>market for chlorine, liquid</t>
+          <t>market for graphite</t>
         </is>
       </c>
       <c r="B2141">
-        <v>1.6362268470439452</v>
+        <v>0.27718928998370695</v>
       </c>
       <c r="C2141" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2141" t="inlineStr">
@@ -54681,27 +54658,27 @@
       </c>
       <c r="G2141" t="inlineStr">
         <is>
-          <t>chlorine, liquid</t>
+          <t>graphite</t>
         </is>
       </c>
       <c r="I2141" t="inlineStr">
         <is>
-          <t>chlorine, liquid</t>
+          <t>graphite</t>
         </is>
       </c>
     </row>
     <row r="2142">
       <c r="A2142" t="inlineStr">
         <is>
-          <t>market for magnesium</t>
+          <t>market for chlorine, liquid</t>
         </is>
       </c>
       <c r="B2142">
-        <v>0.5609096405839644</v>
+        <v>1.6362268470439452</v>
       </c>
       <c r="C2142" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D2142" t="inlineStr">
@@ -54716,27 +54693,27 @@
       </c>
       <c r="G2142" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>chlorine, liquid</t>
         </is>
       </c>
       <c r="I2142" t="inlineStr">
         <is>
-          <t>magnesium</t>
+          <t>chlorine, liquid</t>
         </is>
       </c>
     </row>
     <row r="2143">
       <c r="A2143" t="inlineStr">
         <is>
-          <t>market for oxygen, liquid</t>
+          <t>market for magnesium</t>
         </is>
       </c>
       <c r="B2143">
-        <v>0.3692241653858403</v>
+        <v>0.5609096405839644</v>
       </c>
       <c r="C2143" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2143" t="inlineStr">
@@ -54751,32 +54728,32 @@
       </c>
       <c r="G2143" t="inlineStr">
         <is>
-          <t>oxygen, liquid</t>
+          <t>magnesium</t>
         </is>
       </c>
       <c r="I2143" t="inlineStr">
         <is>
-          <t>oxygen, liquid</t>
+          <t>magnesium</t>
         </is>
       </c>
     </row>
     <row r="2144">
       <c r="A2144" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for oxygen, liquid</t>
         </is>
       </c>
       <c r="B2144">
-        <v>10</v>
+        <v>0.3692241653858403</v>
       </c>
       <c r="C2144" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D2144" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2144" t="inlineStr">
@@ -54786,32 +54763,32 @@
       </c>
       <c r="G2144" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>oxygen, liquid</t>
         </is>
       </c>
       <c r="I2144" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>oxygen, liquid</t>
         </is>
       </c>
     </row>
     <row r="2145">
       <c r="A2145" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market group for electricity, medium voltage</t>
         </is>
       </c>
       <c r="B2145">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C2145" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2145" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F2145" t="inlineStr">
@@ -54821,23 +54798,23 @@
       </c>
       <c r="G2145" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
       <c r="I2145" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="2146">
       <c r="A2146" t="inlineStr">
         <is>
-          <t>market for hazardous waste, for incineration</t>
+          <t>market for heat, district or industrial, natural gas</t>
         </is>
       </c>
       <c r="B2146">
-        <v>-2.249768066575278</v>
+        <v>30</v>
       </c>
       <c r="C2146" t="inlineStr">
         <is>
@@ -54846,7 +54823,7 @@
       </c>
       <c r="D2146" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>megajoule</t>
         </is>
       </c>
       <c r="F2146" t="inlineStr">
@@ -54856,40 +54833,75 @@
       </c>
       <c r="G2146" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
       <c r="I2146" t="inlineStr">
         <is>
-          <t>hazardous waste, for incineration</t>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>
     <row r="2147">
       <c r="A2147" t="inlineStr">
         <is>
-          <t>Carbon dioxide, fossil</t>
+          <t>market for hazardous waste, for incineration</t>
         </is>
       </c>
       <c r="B2147">
-        <v>1.0156376207553877</v>
+        <v>-2.249768066575278</v>
+      </c>
+      <c r="C2147" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
       </c>
       <c r="D2147" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E2147" t="inlineStr">
+      <c r="F2147" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2147" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I2147" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="2148">
+      <c r="A2148" t="inlineStr">
+        <is>
+          <t>Carbon dioxide, fossil</t>
+        </is>
+      </c>
+      <c r="B2148">
+        <v>1.0156376207553877</v>
+      </c>
+      <c r="D2148" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E2148" t="inlineStr">
         <is>
           <t>air::non-urban air or from high stacks</t>
         </is>
       </c>
-      <c r="F2147" t="inlineStr">
+      <c r="F2148" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H2147" t="inlineStr">
+      <c r="H2148" t="inlineStr">
         <is>
           <t>APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
 Replace the explicit 0.6kg chromium-as-zirconium placeholder in all four FR/RER UO2/MOX fuel-fabrication variants. The functional reference is 1kg heavy metal, not 1kg finished oxide or whole assembly. Adopt the published EPR assembly: 527.5kgU, 598kgUO2, 162.02kgM5, 4.359999999999999kgInconel718, 14.6kg304L steel and 0.595kg alumina. Use the detailed Table B9 values rather than mixing its precise rows with rounded B10 totals. Source material total differs slightly from rounded780kg total; do not renormalize metal shares to fill that rounding. PerkgHM these nonfuel components total 0.344218009478673kg. All are supplied once; no extra chromium cladding input remains.
@@ -54900,83 +54912,83 @@
         </is>
       </c>
     </row>
-    <row r="2150">
-      <c r="A2150" t="inlineStr">
+    <row r="2151">
+      <c r="A2151" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2150" t="inlineStr">
+      <c r="B2151" t="inlineStr">
         <is>
           <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
     </row>
-    <row r="2151">
-      <c r="A2151" t="inlineStr">
+    <row r="2152">
+      <c r="A2152" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B2151" t="inlineStr">
+      <c r="B2152" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
     </row>
-    <row r="2152">
-      <c r="A2152" t="inlineStr">
+    <row r="2153">
+      <c r="A2153" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B2152">
+      <c r="B2153">
         <v>1</v>
       </c>
     </row>
-    <row r="2153">
-      <c r="A2153" t="inlineStr">
+    <row r="2154">
+      <c r="A2154" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B2153" t="inlineStr">
+      <c r="B2154" t="inlineStr">
         <is>
           <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
-    <row r="2154">
-      <c r="A2154" t="inlineStr">
+    <row r="2155">
+      <c r="A2155" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B2154" t="inlineStr">
+      <c r="B2155" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
     </row>
-    <row r="2155">
-      <c r="A2155" t="inlineStr">
+    <row r="2156">
+      <c r="A2156" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B2155" t="inlineStr">
+      <c r="B2156" t="inlineStr">
         <is>
           <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
         </is>
       </c>
     </row>
-    <row r="2156">
-      <c r="A2156" t="inlineStr">
+    <row r="2157">
+      <c r="A2157" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B2156" t="inlineStr">
+      <c r="B2157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: niobium metal equivalent, ferroniobium feed and separation reference. Former reference product: niobium metal equivalent, ferroniobium feed and separation reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
@@ -54988,142 +55000,84 @@
         </is>
       </c>
     </row>
-    <row r="2157">
-      <c r="A2157" t="inlineStr">
+    <row r="2158">
+      <c r="A2158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B2158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2159">
+      <c r="A2159" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="2158">
-      <c r="A2158" t="inlineStr">
+    <row r="2160">
+      <c r="A2160" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2158" t="inlineStr">
+      <c r="B2160" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C2158" t="inlineStr">
+      <c r="C2160" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D2158" t="inlineStr">
+      <c r="D2160" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2158" t="inlineStr">
+      <c r="E2160" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F2158" t="inlineStr">
+      <c r="F2160" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2158" t="inlineStr">
+      <c r="G2160" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H2158" t="inlineStr">
+      <c r="H2160" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I2158" t="inlineStr">
+      <c r="I2160" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="2159">
-      <c r="A2159" t="inlineStr">
+    <row r="2161">
+      <c r="A2161" t="inlineStr">
         <is>
           <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
-      <c r="B2159">
+      <c r="B2161">
         <v>1</v>
       </c>
-      <c r="C2159" t="inlineStr">
+      <c r="C2161" t="inlineStr">
         <is>
           <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2159" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2159" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G2159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
-        </is>
-      </c>
-      <c r="I2159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2160">
-      <c r="A2160" t="inlineStr">
-        <is>
-          <t>market for ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-      <c r="B2160">
-        <v>1.5151515151515151</v>
-      </c>
-      <c r="C2160" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2160" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2160" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2160" t="inlineStr">
-        <is>
-          <t>ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-      <c r="I2160" t="inlineStr">
-        <is>
-          <t>ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-    </row>
-    <row r="2161">
-      <c r="A2161" t="inlineStr">
-        <is>
-          <t>market for inert waste, for final disposal</t>
-        </is>
-      </c>
-      <c r="B2161">
-        <v>-0.5151515151515151</v>
-      </c>
-      <c r="C2161" t="inlineStr">
-        <is>
-          <t>RoW</t>
         </is>
       </c>
       <c r="D2161" t="inlineStr">
@@ -55133,28 +55087,28 @@
       </c>
       <c r="F2161" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G2161" t="inlineStr">
         <is>
-          <t>inert waste, for final disposal</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
       <c r="I2161" t="inlineStr">
         <is>
-          <t>inert waste, for final disposal</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
     <row r="2162">
       <c r="A2162" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for ferroniobium, 66% Nb</t>
         </is>
       </c>
       <c r="B2162">
-        <v>5</v>
+        <v>1.5151515151515151</v>
       </c>
       <c r="C2162" t="inlineStr">
         <is>
@@ -55163,7 +55117,7 @@
       </c>
       <c r="D2162" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2162" t="inlineStr">
@@ -55173,92 +55127,162 @@
       </c>
       <c r="G2162" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>ferroniobium, 66% Nb</t>
         </is>
       </c>
       <c r="I2162" t="inlineStr">
+        <is>
+          <t>ferroniobium, 66% Nb</t>
+        </is>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B2163">
+        <v>-0.5151515151515151</v>
+      </c>
+      <c r="C2163" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2163" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2163" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2163" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I2163" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2164">
+        <v>5</v>
+      </c>
+      <c r="C2164" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2164" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2164" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2164" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>
       </c>
-    </row>
-    <row r="2165">
-      <c r="A2165" t="inlineStr">
+      <c r="I2164" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2165" t="inlineStr">
+      <c r="B2167" t="inlineStr">
         <is>
-          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
+          <t xml:space="preserve">zirconium cladding alloy production, epr, m5 type</t>
         </is>
       </c>
     </row>
-    <row r="2166">
-      <c r="A2166" t="inlineStr">
+    <row r="2168">
+      <c r="A2168" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B2166" t="inlineStr">
+      <c r="B2168" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
     </row>
-    <row r="2167">
-      <c r="A2167" t="inlineStr">
+    <row r="2169">
+      <c r="A2169" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B2167">
+      <c r="B2169">
         <v>1</v>
       </c>
     </row>
-    <row r="2168">
-      <c r="A2168" t="inlineStr">
+    <row r="2170">
+      <c r="A2170" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B2168" t="inlineStr">
+      <c r="B2170" t="inlineStr">
         <is>
           <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
-    <row r="2169">
-      <c r="A2169" t="inlineStr">
+    <row r="2171">
+      <c r="A2171" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B2169" t="inlineStr">
+      <c r="B2171" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
     </row>
-    <row r="2170">
-      <c r="A2170" t="inlineStr">
+    <row r="2172">
+      <c r="A2172" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B2170" t="inlineStr">
+      <c r="B2172" t="inlineStr">
         <is>
           <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
         </is>
       </c>
     </row>
-    <row r="2171">
-      <c r="A2171" t="inlineStr">
+    <row r="2173">
+      <c r="A2173" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B2171" t="inlineStr">
+      <c r="B2173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR M5-type zirconium cladding, nominal alloy reference. Former reference product: EPR M5-type zirconium cladding, nominal alloy reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
@@ -55270,173 +55294,80 @@
         </is>
       </c>
     </row>
-    <row r="2172">
-      <c r="A2172" t="inlineStr">
+    <row r="2174">
+      <c r="A2174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B2174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="2173">
-      <c r="A2173" t="inlineStr">
+    <row r="2176">
+      <c r="A2176" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2173" t="inlineStr">
+      <c r="B2176" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C2173" t="inlineStr">
+      <c r="C2176" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D2173" t="inlineStr">
+      <c r="D2176" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2173" t="inlineStr">
+      <c r="E2176" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F2173" t="inlineStr">
+      <c r="F2176" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2173" t="inlineStr">
+      <c r="G2176" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H2173" t="inlineStr">
+      <c r="H2176" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I2173" t="inlineStr">
+      <c r="I2176" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="2174">
-      <c r="A2174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
-        </is>
-      </c>
-      <c r="B2174">
-        <v>1</v>
-      </c>
-      <c r="C2174" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2174" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2174" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G2174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
-        </is>
-      </c>
-      <c r="I2174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2175">
-      <c r="A2175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal production, cladding, Kroll process</t>
-        </is>
-      </c>
-      <c r="B2175">
-        <v>0.9884</v>
-      </c>
-      <c r="C2175" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2175" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2175" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
-        </is>
-      </c>
-      <c r="I2175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
-        </is>
-      </c>
-    </row>
-    <row r="2176">
-      <c r="A2176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
-        </is>
-      </c>
-      <c r="B2176">
-        <v>0.01</v>
-      </c>
-      <c r="C2176" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2176" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2176" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
-        </is>
-      </c>
-      <c r="I2176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
-        </is>
-      </c>
-    </row>
     <row r="2177">
       <c r="A2177" t="inlineStr">
         <is>
-          <t>market for steel, unalloyed</t>
+          <t xml:space="preserve">zirconium cladding alloy production, epr, m5 type</t>
         </is>
       </c>
       <c r="B2177">
-        <v>0.00035</v>
+        <v>1</v>
       </c>
       <c r="C2177" t="inlineStr">
         <is>
@@ -55450,32 +55381,32 @@
       </c>
       <c r="F2177" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G2177" t="inlineStr">
         <is>
-          <t>steel, unalloyed</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
       <c r="I2177" t="inlineStr">
         <is>
-          <t>steel, unalloyed</t>
+          <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
     <row r="2178">
       <c r="A2178" t="inlineStr">
         <is>
-          <t>market for oxygen, liquid</t>
+          <t xml:space="preserve">zirconium metal production, cladding, kroll process</t>
         </is>
       </c>
       <c r="B2178">
-        <v>0.00125</v>
+        <v>0.9884</v>
       </c>
       <c r="C2178" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2178" t="inlineStr">
@@ -55490,23 +55421,23 @@
       </c>
       <c r="G2178" t="inlineStr">
         <is>
-          <t>oxygen, liquid</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
       <c r="I2178" t="inlineStr">
         <is>
-          <t>oxygen, liquid</t>
+          <t xml:space="preserve">zirconium metal, cladding, Kroll process</t>
         </is>
       </c>
     </row>
     <row r="2179">
       <c r="A2179" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t xml:space="preserve">niobium metal production, ferroniobium separation</t>
         </is>
       </c>
       <c r="B2179">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="C2179" t="inlineStr">
         <is>
@@ -55515,7 +55446,7 @@
       </c>
       <c r="D2179" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2179" t="inlineStr">
@@ -55525,32 +55456,32 @@
       </c>
       <c r="G2179" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
       <c r="I2179" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">niobium metal, from ferroniobium separation</t>
         </is>
       </c>
     </row>
     <row r="2180">
       <c r="A2180" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market for steel, unalloyed</t>
         </is>
       </c>
       <c r="B2180">
-        <v>3</v>
+        <v>0.00035</v>
       </c>
       <c r="C2180" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2180" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2180" t="inlineStr">
@@ -55560,23 +55491,23 @@
       </c>
       <c r="G2180" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>steel, unalloyed</t>
         </is>
       </c>
       <c r="I2180" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>steel, unalloyed</t>
         </is>
       </c>
     </row>
     <row r="2181">
       <c r="A2181" t="inlineStr">
         <is>
-          <t>metal working, average for metal product manufacturing</t>
+          <t>market for oxygen, liquid</t>
         </is>
       </c>
       <c r="B2181">
-        <v>1</v>
+        <v>0.00125</v>
       </c>
       <c r="C2181" t="inlineStr">
         <is>
@@ -55595,92 +55526,197 @@
       </c>
       <c r="G2181" t="inlineStr">
         <is>
-          <t>metal working, average for metal product manufacturing</t>
+          <t>oxygen, liquid</t>
         </is>
       </c>
       <c r="I2181" t="inlineStr">
+        <is>
+          <t>oxygen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2182">
+        <v>1</v>
+      </c>
+      <c r="C2182" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2182" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2182" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2182" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2182" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B2183">
+        <v>3</v>
+      </c>
+      <c r="C2183" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2183" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F2183" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2183" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I2183" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" t="inlineStr">
         <is>
           <t>metal working, average for metal product manufacturing</t>
         </is>
       </c>
-    </row>
-    <row r="2184">
-      <c r="A2184" t="inlineStr">
+      <c r="B2184">
+        <v>1</v>
+      </c>
+      <c r="C2184" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2184" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2184" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2184" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="I2184" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2184" t="inlineStr">
+      <c r="B2187" t="inlineStr">
         <is>
-          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
+          <t xml:space="preserve">nickel alloy production, epr springs, inconel 718 type</t>
         </is>
       </c>
     </row>
-    <row r="2185">
-      <c r="A2185" t="inlineStr">
+    <row r="2188">
+      <c r="A2188" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B2185" t="inlineStr">
+      <c r="B2188" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
     </row>
-    <row r="2186">
-      <c r="A2186" t="inlineStr">
+    <row r="2189">
+      <c r="A2189" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B2186">
+      <c r="B2189">
         <v>1</v>
       </c>
     </row>
-    <row r="2187">
-      <c r="A2187" t="inlineStr">
+    <row r="2190">
+      <c r="A2190" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B2187" t="inlineStr">
+      <c r="B2190" t="inlineStr">
         <is>
           <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
-    <row r="2188">
-      <c r="A2188" t="inlineStr">
+    <row r="2191">
+      <c r="A2191" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B2188" t="inlineStr">
+      <c r="B2191" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
     </row>
-    <row r="2189">
-      <c r="A2189" t="inlineStr">
+    <row r="2192">
+      <c r="A2192" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B2189" t="inlineStr">
+      <c r="B2192" t="inlineStr">
         <is>
           <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
         </is>
       </c>
     </row>
-    <row r="2190">
-      <c r="A2190" t="inlineStr">
+    <row r="2193">
+      <c r="A2193" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B2190" t="inlineStr">
+      <c r="B2193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: EPR Inconel718-type spring alloy, nominal reference. Former reference product: EPR Inconel718-type spring alloy, nominal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED EPR FUEL-ASSEMBLY METAL IDENTITY AND DOSE, issue 118, 2026-10-19. EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .
@@ -55692,208 +55728,80 @@
         </is>
       </c>
     </row>
-    <row r="2191">
-      <c r="A2191" t="inlineStr">
+    <row r="2194">
+      <c r="A2194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B2194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="2192">
-      <c r="A2192" t="inlineStr">
+    <row r="2196">
+      <c r="A2196" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2192" t="inlineStr">
+      <c r="B2196" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C2192" t="inlineStr">
+      <c r="C2196" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D2192" t="inlineStr">
+      <c r="D2196" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2192" t="inlineStr">
+      <c r="E2196" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F2192" t="inlineStr">
+      <c r="F2196" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2192" t="inlineStr">
+      <c r="G2196" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H2192" t="inlineStr">
+      <c r="H2196" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I2192" t="inlineStr">
+      <c r="I2196" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="2193">
-      <c r="A2193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
-        </is>
-      </c>
-      <c r="B2193">
-        <v>1</v>
-      </c>
-      <c r="C2193" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2193" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2193" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G2193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
-        </is>
-      </c>
-      <c r="I2193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2194">
-      <c r="A2194" t="inlineStr">
-        <is>
-          <t>market for nickel, class 1</t>
-        </is>
-      </c>
-      <c r="B2194">
-        <v>0.525</v>
-      </c>
-      <c r="C2194" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2194" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2194" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2194" t="inlineStr">
-        <is>
-          <t>nickel, class 1</t>
-        </is>
-      </c>
-      <c r="I2194" t="inlineStr">
-        <is>
-          <t>nickel, class 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2195">
-      <c r="A2195" t="inlineStr">
-        <is>
-          <t>market for chromium</t>
-        </is>
-      </c>
-      <c r="B2195">
-        <v>0.19</v>
-      </c>
-      <c r="C2195" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2195" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2195" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2195" t="inlineStr">
-        <is>
-          <t>chromium</t>
-        </is>
-      </c>
-      <c r="I2195" t="inlineStr">
-        <is>
-          <t>chromium</t>
-        </is>
-      </c>
-    </row>
-    <row r="2196">
-      <c r="A2196" t="inlineStr">
-        <is>
-          <t>market for ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-      <c r="B2196">
-        <v>0.07765151515151514</v>
-      </c>
-      <c r="C2196" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D2196" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F2196" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G2196" t="inlineStr">
-        <is>
-          <t>ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-      <c r="I2196" t="inlineStr">
-        <is>
-          <t>ferroniobium, 66% Nb</t>
-        </is>
-      </c>
-    </row>
     <row r="2197">
       <c r="A2197" t="inlineStr">
         <is>
-          <t>market for molybdenum</t>
+          <t xml:space="preserve">nickel alloy production, epr springs, inconel 718 type</t>
         </is>
       </c>
       <c r="B2197">
-        <v>0.0305</v>
+        <v>1</v>
       </c>
       <c r="C2197" t="inlineStr">
         <is>
@@ -55907,28 +55815,28 @@
       </c>
       <c r="F2197" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G2197" t="inlineStr">
         <is>
-          <t>molybdenum</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
       <c r="I2197" t="inlineStr">
         <is>
-          <t>molybdenum</t>
+          <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
     <row r="2198">
       <c r="A2198" t="inlineStr">
         <is>
-          <t>market for titanium</t>
+          <t>market for nickel, class 1</t>
         </is>
       </c>
       <c r="B2198">
-        <v>0.009</v>
+        <v>0.525</v>
       </c>
       <c r="C2198" t="inlineStr">
         <is>
@@ -55947,27 +55855,27 @@
       </c>
       <c r="G2198" t="inlineStr">
         <is>
-          <t>titanium</t>
+          <t>nickel, class 1</t>
         </is>
       </c>
       <c r="I2198" t="inlineStr">
         <is>
-          <t>titanium</t>
+          <t>nickel, class 1</t>
         </is>
       </c>
     </row>
     <row r="2199">
       <c r="A2199" t="inlineStr">
         <is>
-          <t>market for aluminium, primary, ingot</t>
+          <t>market for chromium</t>
         </is>
       </c>
       <c r="B2199">
-        <v>0.005</v>
+        <v>0.19</v>
       </c>
       <c r="C2199" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2199" t="inlineStr">
@@ -55982,23 +55890,23 @@
       </c>
       <c r="G2199" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t>chromium</t>
         </is>
       </c>
       <c r="I2199" t="inlineStr">
         <is>
-          <t>aluminium, primary, ingot</t>
+          <t>chromium</t>
         </is>
       </c>
     </row>
     <row r="2200">
       <c r="A2200" t="inlineStr">
         <is>
-          <t>market for graphite</t>
+          <t>market for ferroniobium, 66% Nb</t>
         </is>
       </c>
       <c r="B2200">
-        <v>0.0004</v>
+        <v>0.07765151515151514</v>
       </c>
       <c r="C2200" t="inlineStr">
         <is>
@@ -56017,23 +55925,23 @@
       </c>
       <c r="G2200" t="inlineStr">
         <is>
-          <t>graphite</t>
+          <t>ferroniobium, 66% Nb</t>
         </is>
       </c>
       <c r="I2200" t="inlineStr">
         <is>
-          <t>graphite</t>
+          <t>ferroniobium, 66% Nb</t>
         </is>
       </c>
     </row>
     <row r="2201">
       <c r="A2201" t="inlineStr">
         <is>
-          <t>market for steel, unalloyed</t>
+          <t>market for molybdenum</t>
         </is>
       </c>
       <c r="B2201">
-        <v>0.16244848484848481</v>
+        <v>0.0305</v>
       </c>
       <c r="C2201" t="inlineStr">
         <is>
@@ -56052,23 +55960,23 @@
       </c>
       <c r="G2201" t="inlineStr">
         <is>
-          <t>steel, unalloyed</t>
+          <t>molybdenum</t>
         </is>
       </c>
       <c r="I2201" t="inlineStr">
         <is>
-          <t>steel, unalloyed</t>
+          <t>molybdenum</t>
         </is>
       </c>
     </row>
     <row r="2202">
       <c r="A2202" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for titanium</t>
         </is>
       </c>
       <c r="B2202">
-        <v>1</v>
+        <v>0.009</v>
       </c>
       <c r="C2202" t="inlineStr">
         <is>
@@ -56077,7 +55985,7 @@
       </c>
       <c r="D2202" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2202" t="inlineStr">
@@ -56087,23 +55995,23 @@
       </c>
       <c r="G2202" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>titanium</t>
         </is>
       </c>
       <c r="I2202" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>titanium</t>
         </is>
       </c>
     </row>
     <row r="2203">
       <c r="A2203" t="inlineStr">
         <is>
-          <t>market for heat, district or industrial, natural gas</t>
+          <t>market for aluminium, primary, ingot</t>
         </is>
       </c>
       <c r="B2203">
-        <v>3</v>
+        <v>0.005</v>
       </c>
       <c r="C2203" t="inlineStr">
         <is>
@@ -56112,7 +56020,7 @@
       </c>
       <c r="D2203" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F2203" t="inlineStr">
@@ -56122,27 +56030,27 @@
       </c>
       <c r="G2203" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>aluminium, primary, ingot</t>
         </is>
       </c>
       <c r="I2203" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>aluminium, primary, ingot</t>
         </is>
       </c>
     </row>
     <row r="2204">
       <c r="A2204" t="inlineStr">
         <is>
-          <t>metal working, average for metal product manufacturing</t>
+          <t>market for graphite</t>
         </is>
       </c>
       <c r="B2204">
-        <v>1</v>
+        <v>0.0004</v>
       </c>
       <c r="C2204" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D2204" t="inlineStr">
@@ -56157,92 +56065,232 @@
       </c>
       <c r="G2204" t="inlineStr">
         <is>
-          <t>metal working, average for metal product manufacturing</t>
+          <t>graphite</t>
         </is>
       </c>
       <c r="I2204" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" t="inlineStr">
+        <is>
+          <t>market for steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="B2205">
+        <v>0.16244848484848481</v>
+      </c>
+      <c r="C2205" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2205" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2205" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2205" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+      <c r="I2205" t="inlineStr">
+        <is>
+          <t>steel, unalloyed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B2206">
+        <v>1</v>
+      </c>
+      <c r="C2206" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D2206" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F2206" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2206" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I2206" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B2207">
+        <v>3</v>
+      </c>
+      <c r="C2207" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D2207" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F2207" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2207" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I2207" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" t="inlineStr">
         <is>
           <t>metal working, average for metal product manufacturing</t>
         </is>
       </c>
-    </row>
-    <row r="2207">
-      <c r="A2207" t="inlineStr">
+      <c r="B2208">
+        <v>1</v>
+      </c>
+      <c r="C2208" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D2208" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F2208" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G2208" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+      <c r="I2208" t="inlineStr">
+        <is>
+          <t>metal working, average for metal product manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B2207" t="inlineStr">
+      <c r="B2211" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
     </row>
-    <row r="2208">
-      <c r="A2208" t="inlineStr">
+    <row r="2212">
+      <c r="A2212" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B2208" t="inlineStr">
+      <c r="B2212" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
     </row>
-    <row r="2209">
-      <c r="A2209" t="inlineStr">
+    <row r="2213">
+      <c r="A2213" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B2209">
+      <c r="B2213">
         <v>1</v>
       </c>
     </row>
-    <row r="2210">
-      <c r="A2210" t="inlineStr">
+    <row r="2214">
+      <c r="A2214" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B2210" t="inlineStr">
+      <c r="B2214" t="inlineStr">
         <is>
           <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
-    <row r="2211">
-      <c r="A2211" t="inlineStr">
+    <row r="2215">
+      <c r="A2215" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B2211" t="inlineStr">
+      <c r="B2215" t="inlineStr">
         <is>
           <t xml:space="preserve">kilogram</t>
         </is>
       </c>
     </row>
-    <row r="2212">
-      <c r="A2212" t="inlineStr">
+    <row r="2216">
+      <c r="A2216" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B2212" t="inlineStr">
+      <c r="B2216" t="inlineStr">
         <is>
           <t>EDF/AREVA/NDA Technical Note 11261814 (October 2009), UK EPR disposability assessment, p24 M5 composition, Table B8 527.5kgU/assembly, Table B9 component masses: https://www.edfenergy.com/sites/default/files/gda_summary_of_disposability_assessment_for_wastes_and_spent_fuel.pdf . Inconel718 ranges: Special Metals SMC-045 (2007), https://www.specialmetals.com/documents/technical-bulletins/inconel/inconel-alloy-718.pdf .</t>
         </is>
       </c>
     </row>
-    <row r="2213">
-      <c r="A2213" t="inlineStr">
+    <row r="2217">
+      <c r="A2217" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B2213" t="inlineStr">
+      <c r="B2217" t="inlineStr">
         <is>
           <t xml:space="preserve">APPROVED REFERENCE-UNIT CORRECTION, 2026-10-19. Current reference: One kilogram of finished nonfuel assembly components. Unit field: kilogram. Former reference: 1 unit = 0.34421800947867298 kilogram on the current basis. All supplier/product references and direct purchasers are updated together. Recipes are divided by this conversion factor and consumer doses multiplied by it; physical inputs, emissions and waste per original functional unit are preserved. The four fuel-fabrication buyers now purchase 0.344218009478673 kg of components per kg heavy metal. Their existing lognormal loc is shifted by ln(0.344218009478673); log-space scale and distribution are preserved. No new unit vocabulary, design, lifetime, manufacturing yield, recycling credit, primary/secondary share or runtime code change. Earlier source notes below retain their historical normalization; the current reference and amounts above supersede that normalization.
 Nomenclature revision, 2026-10-19. Former activity name: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Former reference product: EPR fuel-assembly nonfuel materials, per kg heavy-metal reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
@@ -56255,230 +56303,242 @@
         </is>
       </c>
     </row>
-    <row r="2214">
-      <c r="A2214" t="inlineStr">
+    <row r="2218">
+      <c r="A2218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B2218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="2215">
-      <c r="A2215" t="inlineStr">
+    <row r="2220">
+      <c r="A2220" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2215" t="inlineStr">
+      <c r="B2220" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C2215" t="inlineStr">
+      <c r="C2220" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D2215" t="inlineStr">
+      <c r="D2220" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2215" t="inlineStr">
+      <c r="E2220" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F2215" t="inlineStr">
+      <c r="F2220" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G2215" t="inlineStr">
+      <c r="G2220" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H2215" t="inlineStr">
+      <c r="H2220" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I2215" t="inlineStr">
+      <c r="I2220" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="2216">
-      <c r="A2216" t="inlineStr">
+    <row r="2221">
+      <c r="A2221" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuel assembly component production, EPR, without nuclear fuel</t>
+          <t xml:space="preserve">fuel assembly component production, epr, without nuclear fuel</t>
         </is>
       </c>
-      <c r="B2216">
+      <c r="B2221">
         <v>1</v>
       </c>
-      <c r="C2216" t="inlineStr">
+      <c r="C2221" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D2216" t="inlineStr">
+      <c r="D2221" t="inlineStr">
         <is>
           <t xml:space="preserve">kilogram</t>
         </is>
       </c>
-      <c r="F2216" t="inlineStr">
+      <c r="F2221" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="G2216" t="inlineStr">
+      <c r="G2221" t="inlineStr">
         <is>
           <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
-      <c r="I2216" t="inlineStr">
+      <c r="I2221" t="inlineStr">
         <is>
           <t xml:space="preserve">fuel assembly components, EPR, without nuclear fuel</t>
         </is>
       </c>
     </row>
-    <row r="2217">
-      <c r="A2217" t="inlineStr">
+    <row r="2222">
+      <c r="A2222" t="inlineStr">
         <is>
-          <t xml:space="preserve">zirconium cladding alloy production, EPR, M5 type</t>
+          <t xml:space="preserve">zirconium cladding alloy production, epr, m5 type</t>
         </is>
       </c>
-      <c r="B2217">
+      <c r="B2222">
         <v>0.8923034558722291</v>
       </c>
-      <c r="C2217" t="inlineStr">
+      <c r="C2222" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D2217" t="inlineStr">
+      <c r="D2222" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F2217" t="inlineStr">
+      <c r="F2222" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G2217" t="inlineStr">
+      <c r="G2222" t="inlineStr">
         <is>
           <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
-      <c r="I2217" t="inlineStr">
+      <c r="I2222" t="inlineStr">
         <is>
           <t xml:space="preserve">zirconium cladding alloy, EPR, M5 type</t>
         </is>
       </c>
     </row>
-    <row r="2218">
-      <c r="A2218" t="inlineStr">
+    <row r="2223">
+      <c r="A2223" t="inlineStr">
         <is>
-          <t xml:space="preserve">nickel alloy production, EPR springs, Inconel 718 type</t>
+          <t xml:space="preserve">nickel alloy production, epr springs, inconel 718 type</t>
         </is>
       </c>
-      <c r="B2218">
+      <c r="B2223">
         <v>0.024012116205424754</v>
       </c>
-      <c r="C2218" t="inlineStr">
+      <c r="C2223" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D2218" t="inlineStr">
+      <c r="D2223" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F2218" t="inlineStr">
+      <c r="F2223" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G2218" t="inlineStr">
+      <c r="G2223" t="inlineStr">
         <is>
           <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
-      <c r="I2218" t="inlineStr">
+      <c r="I2223" t="inlineStr">
         <is>
           <t xml:space="preserve">nickel alloy, EPR springs, Inconel 718 type</t>
         </is>
       </c>
     </row>
-    <row r="2219">
-      <c r="A2219" t="inlineStr">
+    <row r="2224">
+      <c r="A2224" t="inlineStr">
         <is>
           <t>market for steel, chromium steel 18/8</t>
         </is>
       </c>
-      <c r="B2219">
+      <c r="B2224">
         <v>0.08040754509155995</v>
       </c>
-      <c r="C2219" t="inlineStr">
+      <c r="C2224" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D2219" t="inlineStr">
+      <c r="D2224" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F2219" t="inlineStr">
+      <c r="F2224" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G2219" t="inlineStr">
+      <c r="G2224" t="inlineStr">
         <is>
           <t>steel, chromium steel 18/8</t>
         </is>
       </c>
-      <c r="I2219" t="inlineStr">
+      <c r="I2224" t="inlineStr">
         <is>
           <t>steel, chromium steel 18/8</t>
         </is>
       </c>
     </row>
-    <row r="2220">
-      <c r="A2220" t="inlineStr">
+    <row r="2225">
+      <c r="A2225" t="inlineStr">
         <is>
           <t>market for aluminium oxide, non-metallurgical</t>
         </is>
       </c>
-      <c r="B2220">
+      <c r="B2225">
         <v>0.003276882830786176</v>
       </c>
-      <c r="C2220" t="inlineStr">
+      <c r="C2225" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D2220" t="inlineStr">
+      <c r="D2225" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F2220" t="inlineStr">
+      <c r="F2225" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G2220" t="inlineStr">
+      <c r="G2225" t="inlineStr">
         <is>
           <t>aluminium oxide, non-metallurgical</t>
         </is>
       </c>
-      <c r="I2220" t="inlineStr">
+      <c r="I2225" t="inlineStr">
         <is>
           <t>aluminium oxide, non-metallurgical</t>
         </is>
